--- a/waystar-management-report/WayStar_Управленка_Июль2026.xlsx
+++ b/waystar-management-report/WayStar_Управленка_Июль2026.xlsx
@@ -11,13 +11,13 @@
     <sheet name="ОПиУ" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ОДДС" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Структура затрат" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Выручка·Клиенты" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Клиенты" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Поставщики" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Денежные средства" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Реестр операций" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Реестр операций'!$A$4:$P$442</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Реестр операций'!$A$4:$Q$442</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -51,69 +51,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="0016324F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="007B8794"/>
-      <sz val="8.5"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="002A78D6"/>
-      <sz val="15"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="007B8794"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001E8449"/>
-      <sz val="15"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="007B8794"/>
-      <sz val="15"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0014202B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0016324F"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0014202B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00C0392B"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0014202B"/>
-      <sz val="9.5"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
@@ -125,8 +62,19 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0014202B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="007B8794"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0014202B"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -137,8 +85,19 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="0016324F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="007B8794"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0014202B"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -178,6 +137,47 @@
       <color rgb="006C5CE7"/>
       <sz val="8.5"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0016324F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="007B8794"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="002A78D6"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="007B8794"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001E8449"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="007B8794"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -198,7 +198,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4F7FB"/>
+        <fgColor rgb="002A78D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -208,7 +208,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002A78D6"/>
+        <fgColor rgb="00F4F7FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -219,6 +219,55 @@
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3DF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D3DF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9D3DF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3DF"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="medium">
+        <color rgb="0016324F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3DF"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00C9D3DF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3DF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3DF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D3DF"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00C9D3DF"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="medium">
+        <color rgb="0016324F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0016324F"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -262,55 +311,6 @@
         <color rgb="00C9D3DF"/>
       </bottom>
     </border>
-    <border>
-      <top style="thin">
-        <color rgb="00C9D3DF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C9D3DF"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C9D3DF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00C9D3DF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C9D3DF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C9D3DF"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="medium">
-        <color rgb="0016324F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C9D3DF"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C9D3DF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00C9D3DF"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="00C9D3DF"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="medium">
-        <color rgb="0016324F"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="0016324F"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -323,136 +323,136 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="21" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="23" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="24" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="20" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="23" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -874,16 +874,19 @@
       <c r="F5" s="5" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="6" t="n">
-        <v>1053133894</v>
+      <c r="A6" s="6">
+        <f>'ОПиУ'!C5</f>
+        <v/>
       </c>
       <c r="B6" s="7" t="n"/>
-      <c r="C6" s="8" t="n">
-        <v>242490323</v>
+      <c r="C6" s="8">
+        <f>'ОПиУ'!C13</f>
+        <v/>
       </c>
       <c r="D6" s="7" t="n"/>
-      <c r="E6" s="8" t="n">
-        <v>152617115</v>
+      <c r="E6" s="8">
+        <f>'ОПиУ'!C26</f>
+        <v/>
       </c>
       <c r="F6" s="7" t="n"/>
     </row>
@@ -928,16 +931,19 @@
       <c r="F9" s="5" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>152617115</v>
+      <c r="A10" s="6">
+        <f>'ОДДС'!C12</f>
+        <v/>
       </c>
       <c r="B10" s="7" t="n"/>
-      <c r="C10" s="8" t="n">
-        <v>126645918</v>
+      <c r="C10" s="8">
+        <f>'ОПиУ'!C33</f>
+        <v/>
       </c>
       <c r="D10" s="7" t="n"/>
-      <c r="E10" s="11" t="n">
-        <v>10121197251</v>
+      <c r="E10" s="11">
+        <f>'Денежные средства'!C13</f>
+        <v/>
       </c>
       <c r="F10" s="7" t="n"/>
     </row>
@@ -974,8 +980,9 @@
           <t>Выручка</t>
         </is>
       </c>
-      <c r="C14" s="13" t="n">
-        <v>1053133894</v>
+      <c r="C14" s="13">
+        <f>'ОПиУ'!C5</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -984,8 +991,9 @@
           <t>(−) Себестоимость</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n">
-        <v>-810643571</v>
+      <c r="C15" s="13">
+        <f>'ОПиУ'!C6</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -995,8 +1003,9 @@
         </is>
       </c>
       <c r="B16" s="15" t="n"/>
-      <c r="C16" s="16" t="n">
-        <v>242490323</v>
+      <c r="C16" s="16">
+        <f>'ОПиУ'!C13</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1005,8 +1014,9 @@
           <t>(−) Операционные расходы (ФОТ, админ, налоги)</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n">
-        <v>-89873208</v>
+      <c r="C17" s="13">
+        <f>'ОПиУ'!C15+'ОПиУ'!C18+'ОПиУ'!C25</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1016,8 +1026,9 @@
         </is>
       </c>
       <c r="B18" s="15" t="n"/>
-      <c r="C18" s="16" t="n">
-        <v>152617115</v>
+      <c r="C18" s="16">
+        <f>'ОПиУ'!C26</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1026,8 +1037,9 @@
           <t>(−) Финансовые и прочие (нетто)</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
-        <v>-25971197</v>
+      <c r="C19" s="13">
+        <f>'ОПиУ'!C33-'ОПиУ'!C26</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1037,8 +1049,9 @@
         </is>
       </c>
       <c r="B20" s="15" t="n"/>
-      <c r="C20" s="16" t="n">
-        <v>126645918</v>
+      <c r="C20" s="16">
+        <f>'ОПиУ'!C33</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1132,7 +1145,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Управленческий P&amp;L · кассовый метод · тенге · доля от выручки</t>
+          <t>Управленческий P&amp;L · кассовый метод · тенге · ячейки связаны формулами с листом «Реестр операций»</t>
         </is>
       </c>
     </row>
@@ -1160,11 +1173,13 @@
           <t>ВЫРУЧКА от услуг (ТЭО, аренда вагонов/цистерн)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="n">
-        <v>1053133894</v>
-      </c>
-      <c r="D5" s="22" t="n">
-        <v>1</v>
+      <c r="C5" s="21">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D5" s="22">
+        <f>IF($C$5=0,0,C5/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1173,11 +1188,13 @@
           <t>СЕБЕСТОИМОСТЬ услуг</t>
         </is>
       </c>
-      <c r="C6" s="21" t="n">
-        <v>-810643571</v>
-      </c>
-      <c r="D6" s="22" t="n">
-        <v>-0.7697440714006343</v>
+      <c r="C6" s="21">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D6" s="22">
+        <f>IF($C$5=0,0,C6/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1186,11 +1203,13 @@
           <t xml:space="preserve">    Зарубежные перевозчики/экспедиторы</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n">
-        <v>-369864050</v>
-      </c>
-      <c r="D7" s="22" t="n">
-        <v>-0.3512032532229935</v>
+      <c r="C7" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Зарубежные перевозчики/экспедиторы")</f>
+        <v/>
+      </c>
+      <c r="D7" s="22">
+        <f>IF($C$5=0,0,C7/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1199,11 +1218,13 @@
           <t xml:space="preserve">    Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n">
-        <v>-254594351</v>
-      </c>
-      <c r="D8" s="22" t="n">
-        <v>-0.2417492711706064</v>
+      <c r="C8" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Тариф КТЖ (ж/д перевозки)")</f>
+        <v/>
+      </c>
+      <c r="D8" s="22">
+        <f>IF($C$5=0,0,C8/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1212,11 +1233,13 @@
           <t xml:space="preserve">    Аренда/предоставление вагонов</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n">
-        <v>-102335321</v>
-      </c>
-      <c r="D9" s="22" t="n">
-        <v>-0.09717218421013706</v>
+      <c r="C9" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Аренда/предоставление вагонов")</f>
+        <v/>
+      </c>
+      <c r="D9" s="22">
+        <f>IF($C$5=0,0,C9/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1225,11 +1248,13 @@
           <t xml:space="preserve">    Операторы вагонов (КТТ и др.)</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n">
-        <v>-34538828</v>
-      </c>
-      <c r="D10" s="22" t="n">
-        <v>-0.03279623663104792</v>
+      <c r="C10" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Операторы вагонов (КТТ и др.)")</f>
+        <v/>
+      </c>
+      <c r="D10" s="22">
+        <f>IF($C$5=0,0,C10/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1238,11 +1263,13 @@
           <t xml:space="preserve">    Прочие ж/д и ТЭУ услуги</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n">
-        <v>-43687120</v>
-      </c>
-      <c r="D11" s="22" t="n">
-        <v>-0.04148296834669083</v>
+      <c r="C11" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Прочие ж/д и ТЭУ услуги")</f>
+        <v/>
+      </c>
+      <c r="D11" s="22">
+        <f>IF($C$5=0,0,C11/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1251,11 +1278,13 @@
           <t xml:space="preserve">    Ремонт вагонов и узлов</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n">
-        <v>-5623901</v>
-      </c>
-      <c r="D12" s="22" t="n">
-        <v>-0.00534015781915852</v>
+      <c r="C12" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Ремонт вагонов и узлов")</f>
+        <v/>
+      </c>
+      <c r="D12" s="22">
+        <f>IF($C$5=0,0,C12/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1265,11 +1294,13 @@
         </is>
       </c>
       <c r="B13" s="25" t="n"/>
-      <c r="C13" s="26" t="n">
-        <v>242490323</v>
-      </c>
-      <c r="D13" s="27" t="n">
-        <v>0.2302559285993658</v>
+      <c r="C13" s="26">
+        <f>C5+C6</f>
+        <v/>
+      </c>
+      <c r="D13" s="27">
+        <f>IF($C$5=0,0,C13/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1285,11 +1316,13 @@
           <t xml:space="preserve">    Фонд оплаты труда</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n">
-        <v>-61772833</v>
-      </c>
-      <c r="D15" s="22" t="n">
-        <v>-0.05865620018240145</v>
+      <c r="C15" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"ФОТ")</f>
+        <v/>
+      </c>
+      <c r="D15" s="22">
+        <f>IF($C$5=0,0,C15/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1298,11 +1331,13 @@
           <t xml:space="preserve">        Зарплата</t>
         </is>
       </c>
-      <c r="C16" s="13" t="n">
-        <v>-53198407</v>
-      </c>
-      <c r="D16" s="22" t="n">
-        <v>-0.05051438121064918</v>
+      <c r="C16" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Зарплата")</f>
+        <v/>
+      </c>
+      <c r="D16" s="22">
+        <f>IF($C$5=0,0,C16/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1311,11 +1346,13 @@
           <t xml:space="preserve">        Командировки и подотчёт</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n">
-        <v>-8574426</v>
-      </c>
-      <c r="D17" s="22" t="n">
-        <v>-0.008141818971752271</v>
+      <c r="C17" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Командировки и подотчёт")</f>
+        <v/>
+      </c>
+      <c r="D17" s="22">
+        <f>IF($C$5=0,0,C17/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1324,11 +1361,13 @@
           <t xml:space="preserve">    Административные и офисные</t>
         </is>
       </c>
-      <c r="C18" s="13" t="n">
-        <v>-15307694</v>
-      </c>
-      <c r="D18" s="22" t="n">
-        <v>-0.01453537279882301</v>
+      <c r="C18" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Админ/офис")</f>
+        <v/>
+      </c>
+      <c r="D18" s="22">
+        <f>IF($C$5=0,0,C18/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1337,11 +1376,13 @@
           <t xml:space="preserve">        Офис, аренда помещений, хоз.</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
-        <v>-9626462</v>
-      </c>
-      <c r="D19" s="22" t="n">
-        <v>-0.009140777001442521</v>
+      <c r="C19" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Офис, аренда помещений, хоз.")</f>
+        <v/>
+      </c>
+      <c r="D19" s="22">
+        <f>IF($C$5=0,0,C19/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1350,11 +1391,13 @@
           <t xml:space="preserve">        Проф. услуги (бухг./юр./конс.)</t>
         </is>
       </c>
-      <c r="C20" s="13" t="n">
-        <v>-3729917</v>
-      </c>
-      <c r="D20" s="22" t="n">
-        <v>-0.003541730619786289</v>
+      <c r="C20" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Проф. услуги (бухг./юр./конс.)")</f>
+        <v/>
+      </c>
+      <c r="D20" s="22">
+        <f>IF($C$5=0,0,C20/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1363,11 +1406,13 @@
           <t xml:space="preserve">        Связь и ИТ</t>
         </is>
       </c>
-      <c r="C21" s="13" t="n">
-        <v>-1019895</v>
-      </c>
-      <c r="D21" s="22" t="n">
-        <v>-0.0009684382257265859</v>
+      <c r="C21" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Связь и ИТ")</f>
+        <v/>
+      </c>
+      <c r="D21" s="22">
+        <f>IF($C$5=0,0,C21/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1376,11 +1421,13 @@
           <t xml:space="preserve">        Маркетинг и представит.</t>
         </is>
       </c>
-      <c r="C22" s="13" t="n">
-        <v>-823760</v>
-      </c>
-      <c r="D22" s="22" t="n">
-        <v>-0.0007821987351253651</v>
+      <c r="C22" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Маркетинг и представит.")</f>
+        <v/>
+      </c>
+      <c r="D22" s="22">
+        <f>IF($C$5=0,0,C22/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1389,11 +1436,13 @@
           <t xml:space="preserve">        Хоз. расходы и материалы</t>
         </is>
       </c>
-      <c r="C23" s="13" t="n">
-        <v>-71655</v>
-      </c>
-      <c r="D23" s="22" t="n">
-        <v>-6.803978144776152e-05</v>
+      <c r="C23" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Хоз. расходы и материалы")</f>
+        <v/>
+      </c>
+      <c r="D23" s="22">
+        <f>IF($C$5=0,0,C23/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -1402,11 +1451,13 @@
           <t xml:space="preserve">        Страхование</t>
         </is>
       </c>
-      <c r="C24" s="13" t="n">
-        <v>-36005</v>
-      </c>
-      <c r="D24" s="22" t="n">
-        <v>-3.418843529448962e-05</v>
+      <c r="C24" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Страхование")</f>
+        <v/>
+      </c>
+      <c r="D24" s="22">
+        <f>IF($C$5=0,0,C24/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1415,11 +1466,13 @@
           <t xml:space="preserve">    Налоги и отчисления</t>
         </is>
       </c>
-      <c r="C25" s="13" t="n">
-        <v>-12792682</v>
-      </c>
-      <c r="D25" s="22" t="n">
-        <v>-0.01214725079104062</v>
+      <c r="C25" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Налоги")</f>
+        <v/>
+      </c>
+      <c r="D25" s="22">
+        <f>IF($C$5=0,0,C25/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1429,11 +1482,13 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
-      <c r="C26" s="26" t="n">
-        <v>152617115</v>
-      </c>
-      <c r="D26" s="27" t="n">
-        <v>0.1449171048271007</v>
+      <c r="C26" s="26">
+        <f>C13+C15+C18+C25</f>
+        <v/>
+      </c>
+      <c r="D26" s="27">
+        <f>IF($C$5=0,0,C26/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1449,11 +1504,13 @@
           <t xml:space="preserve">    Проценты по кредиту</t>
         </is>
       </c>
-      <c r="C28" s="13" t="n">
-        <v>-5368167</v>
-      </c>
-      <c r="D28" s="22" t="n">
-        <v>-0.005097325885444979</v>
+      <c r="C28" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Проценты по кредиту")</f>
+        <v/>
+      </c>
+      <c r="D28" s="22">
+        <f>IF($C$5=0,0,C28/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1462,11 +1519,13 @@
           <t xml:space="preserve">    Финансовый лизинг</t>
         </is>
       </c>
-      <c r="C29" s="13" t="n">
-        <v>-6458737</v>
-      </c>
-      <c r="D29" s="22" t="n">
-        <v>-0.006132873536085034</v>
+      <c r="C29" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Финансовый лизинг")</f>
+        <v/>
+      </c>
+      <c r="D29" s="22">
+        <f>IF($C$5=0,0,C29/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1475,11 +1534,13 @@
           <t xml:space="preserve">    Банковские комиссии</t>
         </is>
       </c>
-      <c r="C30" s="13" t="n">
-        <v>-1291491</v>
-      </c>
-      <c r="D30" s="22" t="n">
-        <v>-0.001226331558647392</v>
+      <c r="C30" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Банковские комиссии")</f>
+        <v/>
+      </c>
+      <c r="D30" s="22">
+        <f>IF($C$5=0,0,C30/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1488,11 +1549,13 @@
           <t xml:space="preserve">    Проценты по депозиту (доход)</t>
         </is>
       </c>
-      <c r="C31" s="13" t="n">
-        <v>2620911</v>
-      </c>
-      <c r="D31" s="22" t="n">
-        <v>0.002488677825592641</v>
+      <c r="C31" s="13">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$P$5:$P$442,"Проценты по депозиту")</f>
+        <v/>
+      </c>
+      <c r="D31" s="22">
+        <f>IF($C$5=0,0,C31/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1501,11 +1564,13 @@
           <t>ПРОЧИЕ / РАЗОВЫЕ (возвраты авансов, спонсорство)</t>
         </is>
       </c>
-      <c r="C32" s="21" t="n">
-        <v>-15473713</v>
-      </c>
-      <c r="D32" s="22" t="n">
-        <v>-0.01469301603954145</v>
+      <c r="C32" s="21">
+        <f>-(SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Прочее")-SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Прочее"))</f>
+        <v/>
+      </c>
+      <c r="D32" s="22">
+        <f>IF($C$5=0,0,C32/$C$5)</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -1515,17 +1580,19 @@
         </is>
       </c>
       <c r="B33" s="25" t="n"/>
-      <c r="C33" s="26" t="n">
-        <v>126645918</v>
-      </c>
-      <c r="D33" s="27" t="n">
-        <v>0.1202562356329745</v>
-      </c>
-    </row>
-    <row r="35" ht="42" customHeight="1">
+      <c r="C33" s="26">
+        <f>C26+C28+C29+C30+C31+C32</f>
+        <v/>
+      </c>
+      <c r="D33" s="27">
+        <f>IF($C$5=0,0,C33/$C$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="44" customHeight="1">
       <c r="A35" s="29" t="inlineStr">
         <is>
-          <t>Кассовый метод по банковским выпискам. Тело кредита (66,7 млн ₸) и выданные займы (48,1 млн ₸) — движение денег, отражены в ОДДС, а не в ОПиУ; в прибыли учтены только проценты по кредиту. Не учитывает амортизацию, начисления и незакрытые взаиморасчёты (дебиторская/кредиторская задолженность).</t>
+          <t>Кассовый метод по банковским выпискам. Тело кредита (66,7 млн ₸) и выданные займы (48,1 млн ₸) — движение денег, отражены в ОДДС, а не в ОПиУ; в прибыли учтены только проценты по кредиту. Не учитывает амортизацию, начисления и незакрытые взаиморасчёты. Все суммы — формулы SUMIFS по листу «Реестр операций».</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1632,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Прямой метод · тенге · сверка остатка по 5 счетам</t>
+          <t>Прямой метод · тенге · ячейки связаны с реестром · сверка остатка</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1656,7 @@
         </is>
       </c>
       <c r="C5" s="21" t="n">
-        <v>73256</v>
+        <v>73255.64999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1607,8 +1674,9 @@
           <t>Поступления от клиентов за услуги</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n">
-        <v>1053133894</v>
+      <c r="C7" s="13">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1617,8 +1685,9 @@
           <t>Оплата перевозчикам, КТЖ, аренда вагонов (себестоимость)</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n">
-        <v>-810643571</v>
+      <c r="C8" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1627,8 +1696,9 @@
           <t>Оплата труда и командировки</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n">
-        <v>-61772833</v>
+      <c r="C9" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"ФОТ")</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1637,8 +1707,9 @@
           <t>Административные и офисные расходы</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n">
-        <v>-15307694</v>
+      <c r="C10" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Админ/офис")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1647,8 +1718,9 @@
           <t>Налоги и отчисления</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n">
-        <v>-12792682</v>
+      <c r="C11" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Налоги")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1658,8 +1730,9 @@
         </is>
       </c>
       <c r="B12" s="25" t="n"/>
-      <c r="C12" s="26" t="n">
-        <v>152617115</v>
+      <c r="C12" s="26">
+        <f>SUM(C7:C11)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1677,8 +1750,9 @@
           <t>Выдача займов (связанным лицам)</t>
         </is>
       </c>
-      <c r="C14" s="13" t="n">
-        <v>-48128500</v>
+      <c r="C14" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Выданные займы (связ. лица)")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1687,8 +1761,9 @@
           <t>Возврат ранее выданных займов</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n">
-        <v>6001000</v>
+      <c r="C15" s="13">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$P$5:$P$442,"Возврат выданных займов")</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1698,8 +1773,9 @@
         </is>
       </c>
       <c r="B16" s="25" t="n"/>
-      <c r="C16" s="26" t="n">
-        <v>-42127500</v>
+      <c r="C16" s="26">
+        <f>C14+C15</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1717,8 +1793,9 @@
           <t>Погашение тела кредита</t>
         </is>
       </c>
-      <c r="C18" s="13" t="n">
-        <v>-66666667</v>
+      <c r="C18" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Погашение кредита — тело")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1727,8 +1804,9 @@
           <t>Проценты по кредиту</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
-        <v>-5368167</v>
+      <c r="C19" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Проценты по кредиту")</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1737,8 +1815,9 @@
           <t>Финансовый лизинг</t>
         </is>
       </c>
-      <c r="C20" s="13" t="n">
-        <v>-6458737</v>
+      <c r="C20" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Финансовый лизинг")</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1747,8 +1826,9 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
-      <c r="C21" s="13" t="n">
-        <v>-1291491</v>
+      <c r="C21" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Банковские комиссии")</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1757,8 +1837,9 @@
           <t>Проценты по депозиту (доход)</t>
         </is>
       </c>
-      <c r="C22" s="13" t="n">
-        <v>2620911</v>
+      <c r="C22" s="13">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$P$5:$P$442,"Проценты по депозиту")</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1768,8 +1849,9 @@
         </is>
       </c>
       <c r="B23" s="25" t="n"/>
-      <c r="C23" s="26" t="n">
-        <v>-77164151</v>
+      <c r="C23" s="26">
+        <f>SUM(C18:C22)</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -1787,8 +1869,9 @@
           <t>Возврат средств контрагентам (авансы)</t>
         </is>
       </c>
-      <c r="C25" s="13" t="n">
-        <v>-10000000</v>
+      <c r="C25" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Возврат средств контрагенту")</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1797,8 +1880,9 @@
           <t>Спонсорство / благотворительность</t>
         </is>
       </c>
-      <c r="C26" s="13" t="n">
-        <v>-200000</v>
+      <c r="C26" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Спонсорство / благотвор.")</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1807,8 +1891,9 @@
           <t>Прочие расходы</t>
         </is>
       </c>
-      <c r="C27" s="13" t="n">
-        <v>-5502827</v>
+      <c r="C27" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Прочие расходы")</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1817,8 +1902,9 @@
           <t>Прочие поступления</t>
         </is>
       </c>
-      <c r="C28" s="13" t="n">
-        <v>229114</v>
+      <c r="C28" s="13">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$P$5:$P$442,"Возврат средств")</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1828,8 +1914,9 @@
         </is>
       </c>
       <c r="B29" s="25" t="n"/>
-      <c r="C29" s="26" t="n">
-        <v>-15473713</v>
+      <c r="C29" s="26">
+        <f>SUM(C25:C28)</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1838,8 +1925,9 @@
           <t>Перемещения на прочие счета Группы + конвертация валют (нетто)</t>
         </is>
       </c>
-      <c r="C30" s="21" t="n">
-        <v>-17925007</v>
+      <c r="C30" s="21">
+        <f>(SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$N$5:$N$442,"Внутренний перевод")-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внутренний перевод"))+(SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$N$5:$N$442,"Конвертация валют")-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Конвертация валют"))</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1849,8 +1937,9 @@
         </is>
       </c>
       <c r="B31" s="25" t="n"/>
-      <c r="C31" s="26" t="n">
-        <v>-73256</v>
+      <c r="C31" s="26">
+        <f>C12+C16+C23+C29+C30</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1860,14 +1949,15 @@
         </is>
       </c>
       <c r="B32" s="25" t="n"/>
-      <c r="C32" s="26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="42" customHeight="1">
+      <c r="C32" s="26">
+        <f>C5+C31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="44" customHeight="1">
       <c r="A34" s="29" t="inlineStr">
         <is>
-          <t>Сверка сходится: остаток на начало 73 256 ₸ + чистое изменение = остаток на конец ≈ 0 (см. лист «Денежные средства»). Строка «Перемещения на прочие счета Группы + конвертация» балансирует переводы на счета вне этих выписок и курсовые разницы.</t>
+          <t>Сверка сходится: остаток на начало 73 256 ₸ + чистое изменение = остаток на конец ≈ 0 (см. лист «Денежные средства»). Строка «Перемещения на прочие счета Группы + конвертация» балансирует переводы на счета вне этих выписок и курсовые разницы. Все суммы — формулы по реестру.</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1999,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Внешние платежи · группировка по экономическому смыслу</t>
+          <t>Внешние платежи · формулы SUMIFS по реестру</t>
         </is>
       </c>
     </row>
@@ -1943,14 +2033,17 @@
         </is>
       </c>
       <c r="B5" s="15" t="n"/>
-      <c r="C5" s="16" t="n">
-        <v>810643571</v>
-      </c>
-      <c r="D5" s="35" t="n">
-        <v>0.7763794850429858</v>
-      </c>
-      <c r="E5" s="36" t="n">
-        <v>0.7697440714006343</v>
+      <c r="C5" s="16">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D5" s="35">
+        <f>C5/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E5" s="36">
+        <f>C5/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1960,14 +2053,17 @@
         </is>
       </c>
       <c r="B6" s="38" t="n"/>
-      <c r="C6" s="39" t="n">
-        <v>369864050</v>
-      </c>
-      <c r="D6" s="40" t="n">
-        <v>0.3542307255274358</v>
-      </c>
-      <c r="E6" s="40" t="n">
-        <v>0.3512032532229935</v>
+      <c r="C6" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Зарубежные перевозчики/экспедиторы")</f>
+        <v/>
+      </c>
+      <c r="D6" s="40">
+        <f>C6/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E6" s="40">
+        <f>C6/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1977,14 +2073,17 @@
         </is>
       </c>
       <c r="B7" s="38" t="n"/>
-      <c r="C7" s="39" t="n">
-        <v>254594351</v>
-      </c>
-      <c r="D7" s="40" t="n">
-        <v>0.2438332189027859</v>
-      </c>
-      <c r="E7" s="40" t="n">
-        <v>0.2417492711706064</v>
+      <c r="C7" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Тариф КТЖ (ж/д перевозки)")</f>
+        <v/>
+      </c>
+      <c r="D7" s="40">
+        <f>C7/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E7" s="40">
+        <f>C7/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1994,14 +2093,17 @@
         </is>
       </c>
       <c r="B8" s="38" t="n"/>
-      <c r="C8" s="39" t="n">
-        <v>102335321</v>
-      </c>
-      <c r="D8" s="40" t="n">
-        <v>0.09800983617878659</v>
-      </c>
-      <c r="E8" s="40" t="n">
-        <v>0.09717218421013706</v>
+      <c r="C8" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Аренда/предоставление вагонов")</f>
+        <v/>
+      </c>
+      <c r="D8" s="40">
+        <f>C8/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E8" s="40">
+        <f>C8/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -2011,14 +2113,17 @@
         </is>
       </c>
       <c r="B9" s="38" t="n"/>
-      <c r="C9" s="39" t="n">
-        <v>34538828</v>
-      </c>
-      <c r="D9" s="40" t="n">
-        <v>0.0330789495534917</v>
-      </c>
-      <c r="E9" s="40" t="n">
-        <v>0.03279623663104792</v>
+      <c r="C9" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Операторы вагонов (КТТ и др.)")</f>
+        <v/>
+      </c>
+      <c r="D9" s="40">
+        <f>C9/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E9" s="40">
+        <f>C9/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -2028,14 +2133,17 @@
         </is>
       </c>
       <c r="B10" s="38" t="n"/>
-      <c r="C10" s="39" t="n">
-        <v>43687120</v>
-      </c>
-      <c r="D10" s="40" t="n">
-        <v>0.04184056337641547</v>
-      </c>
-      <c r="E10" s="40" t="n">
-        <v>0.04148296834669083</v>
+      <c r="C10" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Прочие ж/д и ТЭУ услуги")</f>
+        <v/>
+      </c>
+      <c r="D10" s="40">
+        <f>C10/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E10" s="40">
+        <f>C10/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -2045,31 +2153,37 @@
         </is>
       </c>
       <c r="B11" s="38" t="n"/>
-      <c r="C11" s="39" t="n">
-        <v>5623901</v>
-      </c>
-      <c r="D11" s="40" t="n">
-        <v>0.005386191504070285</v>
-      </c>
-      <c r="E11" s="40" t="n">
-        <v>0.00534015781915852</v>
+      <c r="C11" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Ремонт вагонов и узлов")</f>
+        <v/>
+      </c>
+      <c r="D11" s="40">
+        <f>C11/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E11" s="40">
+        <f>C11/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="34" t="inlineStr">
         <is>
-          <t>Фонд оплаты труда</t>
+          <t>ФОТ</t>
         </is>
       </c>
       <c r="B12" s="15" t="n"/>
-      <c r="C12" s="16" t="n">
-        <v>61772833</v>
-      </c>
-      <c r="D12" s="35" t="n">
-        <v>0.05916183337317174</v>
-      </c>
-      <c r="E12" s="36" t="n">
-        <v>0.05865620018240145</v>
+      <c r="C12" s="16">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"ФОТ")</f>
+        <v/>
+      </c>
+      <c r="D12" s="35">
+        <f>C12/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E12" s="36">
+        <f>C12/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -2079,14 +2193,17 @@
         </is>
       </c>
       <c r="B13" s="38" t="n"/>
-      <c r="C13" s="39" t="n">
-        <v>53198407</v>
-      </c>
-      <c r="D13" s="40" t="n">
-        <v>0.05094982959755288</v>
-      </c>
-      <c r="E13" s="40" t="n">
-        <v>0.05051438121064918</v>
+      <c r="C13" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Зарплата")</f>
+        <v/>
+      </c>
+      <c r="D13" s="40">
+        <f>C13/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E13" s="40">
+        <f>C13/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -2096,31 +2213,37 @@
         </is>
       </c>
       <c r="B14" s="38" t="n"/>
-      <c r="C14" s="39" t="n">
-        <v>8574426</v>
-      </c>
-      <c r="D14" s="40" t="n">
-        <v>0.008212003775618858</v>
-      </c>
-      <c r="E14" s="40" t="n">
-        <v>0.008141818971752271</v>
+      <c r="C14" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Командировки и подотчёт")</f>
+        <v/>
+      </c>
+      <c r="D14" s="40">
+        <f>C14/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E14" s="40">
+        <f>C14/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="34" t="inlineStr">
         <is>
-          <t>Административные и офисные</t>
+          <t>Админ/офис</t>
         </is>
       </c>
       <c r="B15" s="15" t="n"/>
-      <c r="C15" s="16" t="n">
-        <v>15307694</v>
-      </c>
-      <c r="D15" s="35" t="n">
-        <v>0.01466067186191353</v>
-      </c>
-      <c r="E15" s="36" t="n">
-        <v>0.01453537279882301</v>
+      <c r="C15" s="16">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Админ/офис")</f>
+        <v/>
+      </c>
+      <c r="D15" s="35">
+        <f>C15/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E15" s="36">
+        <f>C15/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -2130,14 +2253,17 @@
         </is>
       </c>
       <c r="B16" s="38" t="n"/>
-      <c r="C16" s="39" t="n">
-        <v>9626462</v>
-      </c>
-      <c r="D16" s="40" t="n">
-        <v>0.009219573108708018</v>
-      </c>
-      <c r="E16" s="40" t="n">
-        <v>0.009140777001442521</v>
+      <c r="C16" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Офис, аренда помещений, хоз.")</f>
+        <v/>
+      </c>
+      <c r="D16" s="40">
+        <f>C16/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E16" s="40">
+        <f>C16/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -2147,14 +2273,17 @@
         </is>
       </c>
       <c r="B17" s="38" t="n"/>
-      <c r="C17" s="39" t="n">
-        <v>3729917</v>
-      </c>
-      <c r="D17" s="40" t="n">
-        <v>0.003572261348823671</v>
-      </c>
-      <c r="E17" s="40" t="n">
-        <v>0.003541730619786289</v>
+      <c r="C17" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Проф. услуги (бухг./юр./конс.)")</f>
+        <v/>
+      </c>
+      <c r="D17" s="40">
+        <f>C17/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E17" s="40">
+        <f>C17/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -2164,14 +2293,17 @@
         </is>
       </c>
       <c r="B18" s="38" t="n"/>
-      <c r="C18" s="39" t="n">
-        <v>1019895</v>
-      </c>
-      <c r="D18" s="40" t="n">
-        <v>0.0009767864397025223</v>
-      </c>
-      <c r="E18" s="40" t="n">
-        <v>0.0009684382257265859</v>
+      <c r="C18" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Связь и ИТ")</f>
+        <v/>
+      </c>
+      <c r="D18" s="40">
+        <f>C18/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E18" s="40">
+        <f>C18/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -2181,14 +2313,17 @@
         </is>
       </c>
       <c r="B19" s="38" t="n"/>
-      <c r="C19" s="39" t="n">
-        <v>823760</v>
-      </c>
-      <c r="D19" s="40" t="n">
-        <v>0.0007889415115245868</v>
-      </c>
-      <c r="E19" s="40" t="n">
-        <v>0.0007821987351253651</v>
+      <c r="C19" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Маркетинг и представит.")</f>
+        <v/>
+      </c>
+      <c r="D19" s="40">
+        <f>C19/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E19" s="40">
+        <f>C19/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -2198,14 +2333,17 @@
         </is>
       </c>
       <c r="B20" s="38" t="n"/>
-      <c r="C20" s="39" t="n">
-        <v>71655</v>
-      </c>
-      <c r="D20" s="40" t="n">
-        <v>6.862630378786814e-05</v>
-      </c>
-      <c r="E20" s="40" t="n">
-        <v>6.803978144776152e-05</v>
+      <c r="C20" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Хоз. расходы и материалы")</f>
+        <v/>
+      </c>
+      <c r="D20" s="40">
+        <f>C20/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E20" s="40">
+        <f>C20/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -2215,31 +2353,37 @@
         </is>
       </c>
       <c r="B21" s="38" t="n"/>
-      <c r="C21" s="39" t="n">
-        <v>36005</v>
-      </c>
-      <c r="D21" s="40" t="n">
-        <v>3.448314936685776e-05</v>
-      </c>
-      <c r="E21" s="40" t="n">
-        <v>3.418843529448962e-05</v>
+      <c r="C21" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Страхование")</f>
+        <v/>
+      </c>
+      <c r="D21" s="40">
+        <f>C21/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E21" s="40">
+        <f>C21/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="34" t="inlineStr">
         <is>
-          <t>Налоги и отчисления</t>
+          <t>Налоги</t>
         </is>
       </c>
       <c r="B22" s="15" t="n"/>
-      <c r="C22" s="16" t="n">
-        <v>12792682</v>
-      </c>
-      <c r="D22" s="35" t="n">
-        <v>0.01225196356066192</v>
-      </c>
-      <c r="E22" s="36" t="n">
-        <v>0.01214725079104062</v>
+      <c r="C22" s="16">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Налоги")</f>
+        <v/>
+      </c>
+      <c r="D22" s="35">
+        <f>C22/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E22" s="36">
+        <f>C22/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -2249,14 +2393,17 @@
         </is>
       </c>
       <c r="B23" s="38" t="n"/>
-      <c r="C23" s="39" t="n">
-        <v>12792682</v>
-      </c>
-      <c r="D23" s="40" t="n">
-        <v>0.01225196356066192</v>
-      </c>
-      <c r="E23" s="40" t="n">
-        <v>0.01214725079104062</v>
+      <c r="C23" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Налоги и отчисления")</f>
+        <v/>
+      </c>
+      <c r="D23" s="40">
+        <f>C23/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E23" s="40">
+        <f>C23/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -2266,14 +2413,17 @@
         </is>
       </c>
       <c r="B24" s="15" t="n"/>
-      <c r="C24" s="16" t="n">
-        <v>127913562</v>
-      </c>
-      <c r="D24" s="35" t="n">
-        <v>0.1225069421586924</v>
-      </c>
-      <c r="E24" s="36" t="n">
-        <v>0.1214599229484442</v>
+      <c r="C24" s="16">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Финансовые")</f>
+        <v/>
+      </c>
+      <c r="D24" s="35">
+        <f>C24/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E24" s="36">
+        <f>C24/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -2283,14 +2433,17 @@
         </is>
       </c>
       <c r="B25" s="38" t="n"/>
-      <c r="C25" s="39" t="n">
-        <v>66666667</v>
-      </c>
-      <c r="D25" s="40" t="n">
-        <v>0.06384881612476399</v>
-      </c>
-      <c r="E25" s="40" t="n">
-        <v>0.06330312511447307</v>
+      <c r="C25" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Погашение кредита — тело")</f>
+        <v/>
+      </c>
+      <c r="D25" s="40">
+        <f>C25/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E25" s="40">
+        <f>C25/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -2300,14 +2453,17 @@
         </is>
       </c>
       <c r="B26" s="38" t="n"/>
-      <c r="C26" s="39" t="n">
-        <v>48128500</v>
-      </c>
-      <c r="D26" s="40" t="n">
-        <v>0.04609421620060585</v>
-      </c>
-      <c r="E26" s="40" t="n">
-        <v>0.04570026685379374</v>
+      <c r="C26" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Выданные займы (связ. лица)")</f>
+        <v/>
+      </c>
+      <c r="D26" s="40">
+        <f>C26/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E26" s="40">
+        <f>C26/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -2317,14 +2473,17 @@
         </is>
       </c>
       <c r="B27" s="38" t="n"/>
-      <c r="C27" s="39" t="n">
-        <v>6458737</v>
-      </c>
-      <c r="D27" s="40" t="n">
-        <v>0.006185740656781538</v>
-      </c>
-      <c r="E27" s="40" t="n">
-        <v>0.006132873536085034</v>
+      <c r="C27" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Финансовый лизинг")</f>
+        <v/>
+      </c>
+      <c r="D27" s="40">
+        <f>C27/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E27" s="40">
+        <f>C27/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -2334,14 +2493,17 @@
         </is>
       </c>
       <c r="B28" s="38" t="n"/>
-      <c r="C28" s="39" t="n">
-        <v>5368167</v>
-      </c>
-      <c r="D28" s="40" t="n">
-        <v>0.005141266289764364</v>
-      </c>
-      <c r="E28" s="40" t="n">
-        <v>0.005097325885444979</v>
+      <c r="C28" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Проценты по кредиту")</f>
+        <v/>
+      </c>
+      <c r="D28" s="40">
+        <f>C28/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E28" s="40">
+        <f>C28/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -2351,14 +2513,17 @@
         </is>
       </c>
       <c r="B29" s="38" t="n"/>
-      <c r="C29" s="39" t="n">
-        <v>1291491</v>
-      </c>
-      <c r="D29" s="40" t="n">
-        <v>0.001236902886776609</v>
-      </c>
-      <c r="E29" s="40" t="n">
-        <v>0.001226331558647392</v>
+      <c r="C29" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Банковские комиссии")</f>
+        <v/>
+      </c>
+      <c r="D29" s="40">
+        <f>C29/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E29" s="40">
+        <f>C29/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -2368,14 +2533,17 @@
         </is>
       </c>
       <c r="B30" s="15" t="n"/>
-      <c r="C30" s="16" t="n">
-        <v>15702827</v>
-      </c>
-      <c r="D30" s="35" t="n">
-        <v>0.01503910400257473</v>
-      </c>
-      <c r="E30" s="36" t="n">
-        <v>0.01491057062709289</v>
+      <c r="C30" s="16">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Прочее")</f>
+        <v/>
+      </c>
+      <c r="D30" s="35">
+        <f>C30/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E30" s="36">
+        <f>C30/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -2385,14 +2553,17 @@
         </is>
       </c>
       <c r="B31" s="38" t="n"/>
-      <c r="C31" s="39" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="D31" s="40" t="n">
-        <v>0.009577322418235733</v>
-      </c>
-      <c r="E31" s="40" t="n">
-        <v>0.009495468766696187</v>
+      <c r="C31" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Возврат средств контрагенту")</f>
+        <v/>
+      </c>
+      <c r="D31" s="40">
+        <f>C31/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E31" s="40">
+        <f>C31/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -2402,14 +2573,17 @@
         </is>
       </c>
       <c r="B32" s="38" t="n"/>
-      <c r="C32" s="39" t="n">
-        <v>5502827</v>
-      </c>
-      <c r="D32" s="40" t="n">
-        <v>0.005270235135974283</v>
-      </c>
-      <c r="E32" s="40" t="n">
-        <v>0.005225192485062779</v>
+      <c r="C32" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Прочие расходы")</f>
+        <v/>
+      </c>
+      <c r="D32" s="40">
+        <f>C32/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E32" s="40">
+        <f>C32/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -2419,14 +2593,17 @@
         </is>
       </c>
       <c r="B33" s="38" t="n"/>
-      <c r="C33" s="39" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D33" s="40" t="n">
-        <v>0.0001915464483647147</v>
-      </c>
-      <c r="E33" s="40" t="n">
-        <v>0.0001899093753339237</v>
+      <c r="C33" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Спонсорство / благотвор.")</f>
+        <v/>
+      </c>
+      <c r="D33" s="40">
+        <f>C33/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E33" s="40">
+        <f>C33/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -2436,14 +2613,16 @@
         </is>
       </c>
       <c r="B34" s="42" t="n"/>
-      <c r="C34" s="43" t="n">
-        <v>1044133168</v>
+      <c r="C34" s="43">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
       </c>
       <c r="D34" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="E34" s="44" t="n">
-        <v>0.9914533887484364</v>
+      <c r="E34" s="44">
+        <f>C34/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2461,11 +2640,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
@@ -2473,14 +2652,14 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Выручка по клиентам</t>
+          <t>Выручка по клиентам (все 25)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Операционные поступления · топ-10 · доля от выручки</t>
+          <t>Все контрагенты-плательщики за услуги · формулы SUMIFS по реестру</t>
         </is>
       </c>
     </row>
@@ -2512,14 +2691,16 @@
       </c>
       <c r="B5" s="46" t="inlineStr">
         <is>
-          <t>QAZAQ-ASTYQ GROUP</t>
-        </is>
-      </c>
-      <c r="C5" s="39" t="n">
-        <v>517893763</v>
-      </c>
-      <c r="D5" s="40" t="n">
-        <v>0.4917644051033258</v>
+          <t>ТОО «QAZAQ-ASTYQ GROUP»</t>
+        </is>
+      </c>
+      <c r="C5" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО «QAZAQ-ASTYQ GROUP»",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D5" s="40">
+        <f>C5/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -2528,14 +2709,16 @@
       </c>
       <c r="B6" s="46" t="inlineStr">
         <is>
-          <t>ALBATAREEQ TRADING (ОАЭ)</t>
-        </is>
-      </c>
-      <c r="C6" s="39" t="n">
-        <v>216324000</v>
-      </c>
-      <c r="D6" s="40" t="n">
-        <v>0.2054097785486786</v>
+          <t>ALBATAREEQ TRADING LLC (ОАЭ)</t>
+        </is>
+      </c>
+      <c r="C6" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ALBATAREEQ TRADING LLC (ОАЭ)",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D6" s="40">
+        <f>C6/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -2544,14 +2727,16 @@
       </c>
       <c r="B7" s="46" t="inlineStr">
         <is>
-          <t>Altyn Shyghys</t>
-        </is>
-      </c>
-      <c r="C7" s="39" t="n">
-        <v>164066366</v>
-      </c>
-      <c r="D7" s="40" t="n">
-        <v>0.1557887056392212</v>
+          <t>ТОО «Altyn Shyghys»</t>
+        </is>
+      </c>
+      <c r="C7" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО «Altyn Shyghys»",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D7" s="40">
+        <f>C7/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -2563,11 +2748,13 @@
           <t>ТОО ROYAL EXPORT</t>
         </is>
       </c>
-      <c r="C8" s="39" t="n">
-        <v>29484000</v>
-      </c>
-      <c r="D8" s="40" t="n">
-        <v>0.02799644011172704</v>
+      <c r="C8" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ROYAL EXPORT",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D8" s="40">
+        <f>C8/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -2579,11 +2766,13 @@
           <t>ТОО "ШыгысАгроТорг"</t>
         </is>
       </c>
-      <c r="C9" s="39" t="n">
-        <v>22400000</v>
-      </c>
-      <c r="D9" s="40" t="n">
-        <v>0.02126985003739946</v>
+      <c r="C9" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""ШыгысАгроТорг""",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D9" s="40">
+        <f>C9/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -2595,11 +2784,13 @@
           <t>ТОО "Экспорт-М"</t>
         </is>
       </c>
-      <c r="C10" s="39" t="n">
-        <v>16860000</v>
-      </c>
-      <c r="D10" s="40" t="n">
-        <v>0.01600936034064977</v>
+      <c r="C10" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Экспорт-М""",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D10" s="40">
+        <f>C10/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -2611,11 +2802,13 @@
           <t>ТОО REGAL EXPORT</t>
         </is>
       </c>
-      <c r="C11" s="39" t="n">
-        <v>16500000</v>
-      </c>
-      <c r="D11" s="40" t="n">
-        <v>0.01566752346504871</v>
+      <c r="C11" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО REGAL EXPORT",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D11" s="40">
+        <f>C11/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -2627,11 +2820,13 @@
           <t>ТОО East Agro Company</t>
         </is>
       </c>
-      <c r="C12" s="39" t="n">
-        <v>12700440</v>
-      </c>
-      <c r="D12" s="40" t="n">
-        <v>0.01205966313432989</v>
+      <c r="C12" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО East Agro Company",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D12" s="40">
+        <f>C12/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -2640,14 +2835,16 @@
       </c>
       <c r="B13" s="46" t="inlineStr">
         <is>
-          <t>ТОО "УСТЬ-КАМЕНОГОРСКИЙ МАСЛО-ЭКСТ</t>
-        </is>
-      </c>
-      <c r="C13" s="39" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="D13" s="40" t="n">
-        <v>0.01139456252003542</v>
+          <t>ТОО "УСТЬ-КАМЕНОГОРСКИЙ МАСЛО-ЭКСТРАКЦИОННЫЙ</t>
+        </is>
+      </c>
+      <c r="C13" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""УСТЬ-КАМЕНОГОРСКИЙ МАСЛО-ЭКСТРАКЦИОННЫЙ",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D13" s="40">
+        <f>C13/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -2659,25 +2856,299 @@
           <t>ТОО Агро-Трейд-2030</t>
         </is>
       </c>
-      <c r="C14" s="39" t="n">
-        <v>8700000</v>
-      </c>
-      <c r="D14" s="40" t="n">
-        <v>0.008261057827025683</v>
+      <c r="C14" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО Агро-Трейд-2030",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D14" s="40">
+        <f>C14/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="n"/>
-      <c r="B15" s="47" t="inlineStr">
-        <is>
-          <t>ИТОГО топ-10</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="n">
-        <v>1016928569</v>
-      </c>
-      <c r="D15" s="48" t="n">
-        <v>0.9656213467274415</v>
+      <c r="A15" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="46" t="inlineStr">
+        <is>
+          <t>ТОО Евразиан Каспиан Транс</t>
+        </is>
+      </c>
+      <c r="C15" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО Евразиан Каспиан Транс",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D15" s="40">
+        <f>C15/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "GREENLIGHTS (ГРИНЛАЙТС)"</t>
+        </is>
+      </c>
+      <c r="C16" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""GREENLIGHTS (ГРИНЛАЙТС)""",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D16" s="40">
+        <f>C16/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="45" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="46" t="inlineStr">
+        <is>
+          <t>ТОО Темир Экспресс Логистик</t>
+        </is>
+      </c>
+      <c r="C17" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО Темир Экспресс Логистик",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D17" s="40">
+        <f>C17/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="45" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "TimeAgro"</t>
+        </is>
+      </c>
+      <c r="C18" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""TimeAgro""",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D18" s="40">
+        <f>C18/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="46" t="inlineStr">
+        <is>
+          <t>ТОВАРИЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ</t>
+        </is>
+      </c>
+      <c r="C19" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОВАРИЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D19" s="40">
+        <f>C19/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="46" t="inlineStr">
+        <is>
+          <t>ТОО ALTAI MAI</t>
+        </is>
+      </c>
+      <c r="C20" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ALTAI MAI",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D20" s="40">
+        <f>C20/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="45" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="46" t="inlineStr">
+        <is>
+          <t>ТОО «Atasu Global Trans»</t>
+        </is>
+      </c>
+      <c r="C21" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО «Atasu Global Trans»",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D21" s="40">
+        <f>C21/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="45" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="46" t="inlineStr">
+        <is>
+          <t>ТОО Kaz-Smart Logistics</t>
+        </is>
+      </c>
+      <c r="C22" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО Kaz-Smart Logistics",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D22" s="40">
+        <f>C22/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="45" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="46" t="inlineStr">
+        <is>
+          <t>ТОО EASY BOX</t>
+        </is>
+      </c>
+      <c r="C23" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО EASY BOX",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D23" s="40">
+        <f>C23/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "AsstrА Almaty" (АсстрА Алматы)</t>
+        </is>
+      </c>
+      <c r="C24" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""AsstrА Almaty"" (АсстрА Алматы)",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D24" s="40">
+        <f>C24/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="45" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="46" t="inlineStr">
+        <is>
+          <t>ТОО Rhenus Intermodal Systems</t>
+        </is>
+      </c>
+      <c r="C25" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО Rhenus Intermodal Systems",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D25" s="40">
+        <f>C25/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="45" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="46" t="inlineStr">
+        <is>
+          <t>ТОО Каз Алтын Групп</t>
+        </is>
+      </c>
+      <c r="C26" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО Каз Алтын Групп",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D26" s="40">
+        <f>C26/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="45" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "Максат-2030"</t>
+        </is>
+      </c>
+      <c r="C27" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Максат-2030""",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D27" s="40">
+        <f>C27/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="45" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "FRS logistics"</t>
+        </is>
+      </c>
+      <c r="C28" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""FRS logistics""",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D28" s="40">
+        <f>C28/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="45" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="46" t="inlineStr">
+        <is>
+          <t>Данияр Алим</t>
+        </is>
+      </c>
+      <c r="C29" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"Данияр Алим",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D29" s="40">
+        <f>C29/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="25" t="n"/>
+      <c r="B30" s="47" t="inlineStr">
+        <is>
+          <t>ИТОГО (25 контрагентов)</t>
+        </is>
+      </c>
+      <c r="C30" s="26">
+        <f>SUM(C5:C29)</f>
+        <v/>
+      </c>
+      <c r="D30" s="48">
+        <f>C30/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2695,11 +3166,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
@@ -2707,14 +3178,14 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Затраты по поставщикам</t>
+          <t>Затраты по поставщикам (все 24)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Операционные платежи · топ-10 · доля от себестоимости</t>
+          <t>Все поставщики услуг (себестоимость) · формулы SUMIFS по реестру</t>
         </is>
       </c>
     </row>
@@ -2746,14 +3217,16 @@
       </c>
       <c r="B5" s="46" t="inlineStr">
         <is>
-          <t>КТЖ-Грузовые перевозки</t>
-        </is>
-      </c>
-      <c r="C5" s="39" t="n">
-        <v>254594351</v>
-      </c>
-      <c r="D5" s="40" t="n">
-        <v>0.3140644795493091</v>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
+      <c r="C5" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО «КТЖ-Грузовые перевозки»",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D5" s="40">
+        <f>C5/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -2762,14 +3235,16 @@
       </c>
       <c r="B6" s="46" t="inlineStr">
         <is>
-          <t>MEGA STOCK CO (Таиланд)</t>
-        </is>
-      </c>
-      <c r="C6" s="39" t="n">
-        <v>235072080</v>
-      </c>
-      <c r="D6" s="40" t="n">
-        <v>0.2899820442268194</v>
+          <t>MEGA STOCK CO. LTD (Таиланд)</t>
+        </is>
+      </c>
+      <c r="C6" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"MEGA STOCK CO. LTD (Таиланд)",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D6" s="40">
+        <f>C6/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -2778,14 +3253,16 @@
       </c>
       <c r="B7" s="46" t="inlineStr">
         <is>
-          <t>ТрансАльянс Запад (РФ)</t>
-        </is>
-      </c>
-      <c r="C7" s="39" t="n">
-        <v>111821582</v>
-      </c>
-      <c r="D7" s="40" t="n">
-        <v>0.1379417362854883</v>
+          <t>ООО «ТрансАльянс Запад» (РФ)</t>
+        </is>
+      </c>
+      <c r="C7" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ООО «ТрансАльянс Запад» (РФ)",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D7" s="40">
+        <f>C7/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -2794,14 +3271,16 @@
       </c>
       <c r="B8" s="46" t="inlineStr">
         <is>
-          <t>КазТемирТранс (КТТ)</t>
-        </is>
-      </c>
-      <c r="C8" s="39" t="n">
-        <v>34538828</v>
-      </c>
-      <c r="D8" s="40" t="n">
-        <v>0.04260667649102064</v>
+          <t>АО «КазТемирТранс» (КТТ)</t>
+        </is>
+      </c>
+      <c r="C8" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"АО «КазТемирТранс» (КТТ)",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D8" s="40">
+        <f>C8/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -2813,11 +3292,13 @@
           <t>ТОО "АРНА"</t>
         </is>
       </c>
-      <c r="C9" s="39" t="n">
-        <v>33227040</v>
-      </c>
-      <c r="D9" s="40" t="n">
-        <v>0.04098847035686372</v>
+      <c r="C9" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""АРНА""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D9" s="40">
+        <f>C9/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -2829,11 +3310,13 @@
           <t>ТОО «InterLog Co»</t>
         </is>
       </c>
-      <c r="C10" s="39" t="n">
-        <v>27998080</v>
-      </c>
-      <c r="D10" s="40" t="n">
-        <v>0.03453808922278659</v>
+      <c r="C10" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО «InterLog Co»",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D10" s="40">
+        <f>C10/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -2845,11 +3328,13 @@
           <t>ТОО "PRATA"</t>
         </is>
       </c>
-      <c r="C11" s="39" t="n">
-        <v>27590000</v>
-      </c>
-      <c r="D11" s="40" t="n">
-        <v>0.03403468672339967</v>
+      <c r="C11" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""PRATA""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D11" s="40">
+        <f>C11/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -2858,14 +3343,16 @@
       </c>
       <c r="B12" s="46" t="inlineStr">
         <is>
-          <t>LLC Altyn Trans</t>
-        </is>
-      </c>
-      <c r="C12" s="39" t="n">
-        <v>21970490</v>
-      </c>
-      <c r="D12" s="40" t="n">
-        <v>0.02710252834746748</v>
+          <t>LLC Altyn Trans (Узб.)</t>
+        </is>
+      </c>
+      <c r="C12" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"LLC Altyn Trans (Узб.)",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D12" s="40">
+        <f>C12/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -2874,14 +3361,16 @@
       </c>
       <c r="B13" s="46" t="inlineStr">
         <is>
-          <t>ТОО "ResursLogistiс (РесурсЛогисти</t>
-        </is>
-      </c>
-      <c r="C13" s="39" t="n">
-        <v>16724520</v>
-      </c>
-      <c r="D13" s="40" t="n">
-        <v>0.02063116342150172</v>
+          <t>ТОО "ЭДЕМ ТРАНС"</t>
+        </is>
+      </c>
+      <c r="C13" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""ЭДЕМ ТРАНС""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D13" s="40">
+        <f>C13/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -2890,28 +3379,284 @@
       </c>
       <c r="B14" s="46" t="inlineStr">
         <is>
-          <t>ТОО "ЭДЕМ ТРАНС"</t>
-        </is>
-      </c>
-      <c r="C14" s="39" t="n">
-        <v>14449040</v>
-      </c>
-      <c r="D14" s="40" t="n">
-        <v>0.01782415911032515</v>
+          <t>ТОО "PetroComLogistics"</t>
+        </is>
+      </c>
+      <c r="C14" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""PetroComLogistics""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D14" s="40">
+        <f>C14/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="n"/>
-      <c r="B15" s="47" t="inlineStr">
-        <is>
-          <t>ИТОГО топ-10</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="n">
-        <v>777986012</v>
-      </c>
-      <c r="D15" s="48" t="n">
-        <v>0.9597140337349818</v>
+      <c r="A15" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "ЭРСАЛТ РЭЙЛ"</t>
+        </is>
+      </c>
+      <c r="C15" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""ЭРСАЛТ РЭЙЛ""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D15" s="40">
+        <f>C15/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "USM-Logistics"</t>
+        </is>
+      </c>
+      <c r="C16" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""USM-Logistics""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D16" s="40">
+        <f>C16/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="45" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "ResursLogistiс (РесурсЛогистик)"</t>
+        </is>
+      </c>
+      <c r="C17" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""ResursLogistiс (РесурсЛогистик)""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D17" s="40">
+        <f>C17/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="45" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "Нұр-Альфинур"</t>
+        </is>
+      </c>
+      <c r="C18" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Нұр-Альфинур""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D18" s="40">
+        <f>C18/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "Asia Railways Tracking Service (Азия Рэ</t>
+        </is>
+      </c>
+      <c r="C19" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Asia Railways Tracking Service (Азия Рэ",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D19" s="40">
+        <f>C19/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="46" t="inlineStr">
+        <is>
+          <t>Turkmen Demiryol Express (Туркм.)</t>
+        </is>
+      </c>
+      <c r="C20" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"Turkmen Demiryol Express (Туркм.)",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D20" s="40">
+        <f>C20/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="45" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="46" t="inlineStr">
+        <is>
+          <t>ТОО ""SK RAILWAY Service""</t>
+        </is>
+      </c>
+      <c r="C21" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО """"SK RAILWAY Service""""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D21" s="40">
+        <f>C21/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="45" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="46" t="inlineStr">
+        <is>
+          <t>филиал акционерного общества "Национальная к</t>
+        </is>
+      </c>
+      <c r="C22" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"филиал акционерного общества ""Национальная к",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D22" s="40">
+        <f>C22/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="45" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "ТОР Арыс"</t>
+        </is>
+      </c>
+      <c r="C23" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""ТОР Арыс""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D23" s="40">
+        <f>C23/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "Olivin.kz (Оливин.кз)"</t>
+        </is>
+      </c>
+      <c r="C24" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Olivin.kz (Оливин.кз)""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D24" s="40">
+        <f>C24/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="45" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="46" t="inlineStr">
+        <is>
+          <t>Производственный кооператив "ИБРАЕВ+К"</t>
+        </is>
+      </c>
+      <c r="C25" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"Производственный кооператив ""ИБРАЕВ+К""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D25" s="40">
+        <f>C25/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="45" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "Объединенное железнодорожное хозяйство"</t>
+        </is>
+      </c>
+      <c r="C26" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Объединенное железнодорожное хозяйство""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D26" s="40">
+        <f>C26/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="45" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "АФ АГМ-Табыс"</t>
+        </is>
+      </c>
+      <c r="C27" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""АФ АГМ-Табыс""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D27" s="40">
+        <f>C27/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="45" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>Филиал акционерного общества «Национальная к</t>
+        </is>
+      </c>
+      <c r="C28" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"Филиал акционерного общества «Национальная к",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D28" s="40">
+        <f>C28/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="25" t="n"/>
+      <c r="B29" s="47" t="inlineStr">
+        <is>
+          <t>ИТОГО (24 контрагентов)</t>
+        </is>
+      </c>
+      <c r="C29" s="26">
+        <f>SUM(C5:C28)</f>
+        <v/>
+      </c>
+      <c r="D29" s="48">
+        <f>C29/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2951,7 +3696,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Сверка: остаток на начало + приток − отток = остаток на конец</t>
+          <t>Сверка: остаток на начало + приток − отток = остаток на конец · притоки/оттоки — формулы по реестру</t>
         </is>
       </c>
     </row>
@@ -3004,19 +3749,23 @@
         </is>
       </c>
       <c r="C5" s="39" t="n">
-        <v>67512</v>
-      </c>
-      <c r="D5" s="39" t="n">
-        <v>3372821478</v>
-      </c>
-      <c r="E5" s="39" t="n">
-        <v>3372888990</v>
-      </c>
-      <c r="F5" s="45" t="n">
-        <v>319</v>
-      </c>
-      <c r="G5" s="39" t="n">
-        <v>0</v>
+        <v>67511.82000000001</v>
+      </c>
+      <c r="D5" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$B$5:$B$442,"ЦентрКредит",'Реестр операций'!$C$5:$C$442,"KZT")</f>
+        <v/>
+      </c>
+      <c r="E5" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$B$5:$B$442,"ЦентрКредит",'Реестр операций'!$C$5:$C$442,"KZT")</f>
+        <v/>
+      </c>
+      <c r="F5" s="45">
+        <f>COUNTIFS('Реестр операций'!$B$5:$B$442,"ЦентрКредит",'Реестр операций'!$C$5:$C$442,"KZT")</f>
+        <v/>
+      </c>
+      <c r="G5" s="39">
+        <f>C5+D5-E5</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -3033,17 +3782,21 @@
       <c r="C6" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="39" t="n">
-        <v>260477795</v>
-      </c>
-      <c r="E6" s="39" t="n">
-        <v>260477795</v>
-      </c>
-      <c r="F6" s="45" t="n">
-        <v>16</v>
-      </c>
-      <c r="G6" s="39" t="n">
-        <v>0</v>
+      <c r="D6" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$B$5:$B$442,"ЦентрКредит",'Реестр операций'!$C$5:$C$442,"USD")</f>
+        <v/>
+      </c>
+      <c r="E6" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$B$5:$B$442,"ЦентрКредит",'Реестр операций'!$C$5:$C$442,"USD")</f>
+        <v/>
+      </c>
+      <c r="F6" s="45">
+        <f>COUNTIFS('Реестр операций'!$B$5:$B$442,"ЦентрКредит",'Реестр операций'!$C$5:$C$442,"USD")</f>
+        <v/>
+      </c>
+      <c r="G6" s="39">
+        <f>C6+D6-E6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -3060,17 +3813,21 @@
       <c r="C7" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="39" t="n">
-        <v>111821582</v>
-      </c>
-      <c r="E7" s="39" t="n">
-        <v>111821582</v>
-      </c>
-      <c r="F7" s="45" t="n">
-        <v>4</v>
-      </c>
-      <c r="G7" s="39" t="n">
-        <v>0</v>
+      <c r="D7" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$B$5:$B$442,"ЦентрКредит",'Реестр операций'!$C$5:$C$442,"RUB")</f>
+        <v/>
+      </c>
+      <c r="E7" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$B$5:$B$442,"ЦентрКредит",'Реестр операций'!$C$5:$C$442,"RUB")</f>
+        <v/>
+      </c>
+      <c r="F7" s="45">
+        <f>COUNTIFS('Реестр операций'!$B$5:$B$442,"ЦентрКредит",'Реестр операций'!$C$5:$C$442,"RUB")</f>
+        <v/>
+      </c>
+      <c r="G7" s="39">
+        <f>C7+D7-E7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -3085,19 +3842,23 @@
         </is>
       </c>
       <c r="C8" s="39" t="n">
-        <v>5744</v>
-      </c>
-      <c r="D8" s="39" t="n">
-        <v>1099117142</v>
-      </c>
-      <c r="E8" s="39" t="n">
-        <v>1099122886</v>
-      </c>
-      <c r="F8" s="45" t="n">
-        <v>95</v>
-      </c>
-      <c r="G8" s="39" t="n">
-        <v>0</v>
+        <v>5743.83</v>
+      </c>
+      <c r="D8" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$B$5:$B$442,"Bank RBK",'Реестр операций'!$C$5:$C$442,"KZT")</f>
+        <v/>
+      </c>
+      <c r="E8" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$B$5:$B$442,"Bank RBK",'Реестр операций'!$C$5:$C$442,"KZT")</f>
+        <v/>
+      </c>
+      <c r="F8" s="45">
+        <f>COUNTIFS('Реестр операций'!$B$5:$B$442,"Bank RBK",'Реестр операций'!$C$5:$C$442,"KZT")</f>
+        <v/>
+      </c>
+      <c r="G8" s="39">
+        <f>C8+D8-E8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -3114,17 +3875,21 @@
       <c r="C9" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="39" t="n">
-        <v>216324000</v>
-      </c>
-      <c r="E9" s="39" t="n">
-        <v>216324000</v>
-      </c>
-      <c r="F9" s="45" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" s="39" t="n">
-        <v>0</v>
+      <c r="D9" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$B$5:$B$442,"Bank RBK",'Реестр операций'!$C$5:$C$442,"USD")</f>
+        <v/>
+      </c>
+      <c r="E9" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$B$5:$B$442,"Bank RBK",'Реестр операций'!$C$5:$C$442,"USD")</f>
+        <v/>
+      </c>
+      <c r="F9" s="45">
+        <f>COUNTIFS('Реестр операций'!$B$5:$B$442,"Bank RBK",'Реестр операций'!$C$5:$C$442,"USD")</f>
+        <v/>
+      </c>
+      <c r="G9" s="39">
+        <f>C9+D9-E9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -3134,20 +3899,25 @@
         </is>
       </c>
       <c r="B10" s="42" t="n"/>
-      <c r="C10" s="43" t="n">
-        <v>73256</v>
-      </c>
-      <c r="D10" s="43" t="n">
-        <v>5060561998</v>
-      </c>
-      <c r="E10" s="43" t="n">
-        <v>5060635253</v>
-      </c>
-      <c r="F10" s="52" t="n">
-        <v>438</v>
-      </c>
-      <c r="G10" s="43" t="n">
-        <v>0</v>
+      <c r="C10" s="43">
+        <f>SUM(C5:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="43">
+        <f>SUM(D5:D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="43">
+        <f>SUM(E5:E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="52">
+        <f>SUM(F5:F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="43">
+        <f>SUM(G5:G9)</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -3163,38 +3933,42 @@
           <t>Валовой оборот по 5 счетам (приток+отток)</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n">
-        <v>10121197251</v>
+      <c r="C13" s="13">
+        <f>SUM('Реестр операций'!$L$5:$L$442)+SUM('Реестр операций'!$M$5:$M$442)</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в т.ч. «шум» (внутренние переводы + конвертация)</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>8015079164</v>
+          <t>Реальный внешний приток</t>
+        </is>
+      </c>
+      <c r="C14" s="13">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="54" t="inlineStr">
         <is>
-          <t>Реальный внешний приток</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>1061984919</v>
+          <t>Реальный внешний расход</t>
+        </is>
+      </c>
+      <c r="C15" s="13">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="54" t="inlineStr">
         <is>
-          <t>Реальный внешний расход</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>1044133168</v>
+          <t>«Шум» (внутр. переводы + конвертация)</t>
+        </is>
+      </c>
+      <c r="C16" s="13">
+        <f>SUM('Реестр операций'!$L$5:$L$442)+SUM('Реестр операций'!$M$5:$M$442)-SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3212,25 +3986,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P442"/>
+  <dimension ref="A1:Q442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3243,7 +4018,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Все 438 операций из выписок с классификацией · фильтруется по столбцам</t>
+          <t>Все 438 операций из выписок с классификацией · источник для всех формул · фильтруется</t>
         </is>
       </c>
     </row>
@@ -3328,6 +4103,11 @@
           <t>Статья</t>
         </is>
       </c>
+      <c r="Q4" s="19" t="inlineStr">
+        <is>
+          <t>Контрагент (норм.)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="55" t="inlineStr">
@@ -3396,6 +4176,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q5" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Shiny river"</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="55" t="inlineStr">
@@ -3464,6 +4249,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q6" s="55" t="inlineStr">
+        <is>
+          <t>Доолоткулов Данияр Дулатбекович</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="55" t="inlineStr">
@@ -3532,6 +4322,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q7" s="55" t="inlineStr">
+        <is>
+          <t>Унбетпаев Ернар Байтасович</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="55" t="inlineStr">
@@ -3600,6 +4395,11 @@
           <t>Ремонт вагонов и узлов</t>
         </is>
       </c>
+      <c r="Q8" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Olivin.kz (Оливин.кз)"</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="55" t="inlineStr">
@@ -3668,6 +4468,11 @@
           <t>Аренда/предоставление вагонов</t>
         </is>
       </c>
+      <c r="Q9" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Asia Railways Tracking Service (Азия Рэ</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="55" t="inlineStr">
@@ -3736,6 +4541,11 @@
           <t>Ремонт вагонов и узлов</t>
         </is>
       </c>
+      <c r="Q10" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Нұр-Альфинур"</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="55" t="inlineStr">
@@ -3804,6 +4614,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q11" s="55" t="inlineStr">
+        <is>
+          <t>Банк ЦентрКредит для ЗП</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="55" t="inlineStr">
@@ -3872,6 +4687,11 @@
           <t>Аренда/предоставление вагонов</t>
         </is>
       </c>
+      <c r="Q12" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "ResursLogistiс (РесурсЛогистик)"</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="55" t="inlineStr">
@@ -3940,6 +4760,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q13" s="55" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="55" t="inlineStr">
@@ -4008,6 +4829,11 @@
           <t>Возврат средств контрагенту</t>
         </is>
       </c>
+      <c r="Q14" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "ResursLogistiс (РесурсЛогистик)"</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="55" t="inlineStr">
@@ -4076,6 +4902,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q15" s="55" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="55" t="inlineStr">
@@ -4144,6 +4971,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q16" s="55" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="55" t="inlineStr">
@@ -4212,6 +5040,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q17" s="55" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="55" t="inlineStr">
@@ -4280,6 +5109,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q18" s="55" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="55" t="inlineStr">
@@ -4348,6 +5178,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q19" s="55" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="55" t="inlineStr">
@@ -4416,6 +5247,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q20" s="55" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="55" t="inlineStr">
@@ -4484,6 +5316,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q21" s="55" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="55" t="inlineStr">
@@ -4552,6 +5385,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q22" s="55" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="55" t="inlineStr">
@@ -4620,6 +5454,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q23" s="55" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="55" t="inlineStr">
@@ -4688,6 +5523,11 @@
           <t>Налоги и отчисления</t>
         </is>
       </c>
+      <c r="Q24" s="55" t="inlineStr">
+        <is>
+          <t>РГУ  УГД по Алмалинскому району ДГД по город</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="55" t="inlineStr">
@@ -4756,6 +5596,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q25" s="55" t="inlineStr">
+        <is>
+          <t>Индивидуальный предприниматель "Саметханов А</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="55" t="inlineStr">
@@ -4824,6 +5669,11 @@
           <t>Проф. услуги (бухг./юр./конс.)</t>
         </is>
       </c>
+      <c r="Q26" s="55" t="inlineStr">
+        <is>
+          <t>Индивидуальный предприниматель "Капизова"</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="55" t="inlineStr">
@@ -4892,6 +5742,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q27" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное Общество "Банк ЦентрКредит"</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="55" t="inlineStr">
@@ -4960,6 +5815,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q28" s="55" t="inlineStr">
+        <is>
+          <t>Алим</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="55" t="inlineStr">
@@ -5028,6 +5888,11 @@
           <t>Прочие ж/д и ТЭУ услуги</t>
         </is>
       </c>
+      <c r="Q29" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «InterLog Co»</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="55" t="inlineStr">
@@ -5096,6 +5961,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q30" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="55" t="inlineStr">
@@ -5164,6 +6034,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q31" s="55" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="55" t="inlineStr">
@@ -5232,6 +6103,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q32" s="55" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="55" t="inlineStr">
@@ -5300,6 +6172,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q33" s="55" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="55" t="inlineStr">
@@ -5368,6 +6241,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q34" s="55" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="55" t="inlineStr">
@@ -5436,6 +6310,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q35" s="55" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="55" t="inlineStr">
@@ -5504,6 +6379,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q36" s="55" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="55" t="inlineStr">
@@ -5572,6 +6448,11 @@
           <t>Налоги и отчисления</t>
         </is>
       </c>
+      <c r="Q37" s="55" t="inlineStr">
+        <is>
+          <t>УГД по Есильскому району ДГД по городу Астан</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="55" t="inlineStr">
@@ -5640,6 +6521,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q38" s="55" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="55" t="inlineStr">
@@ -5708,6 +6590,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q39" s="55" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="55" t="inlineStr">
@@ -5776,6 +6659,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q40" s="55" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="55" t="inlineStr">
@@ -5844,6 +6728,11 @@
           <t>Налоги и отчисления</t>
         </is>
       </c>
+      <c r="Q41" s="55" t="inlineStr">
+        <is>
+          <t>УГД по Есильскому району ДГД по городу Астан</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="55" t="inlineStr">
@@ -5912,6 +6801,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q42" s="55" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="55" t="inlineStr">
@@ -5980,6 +6870,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q43" s="55" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="55" t="inlineStr">
@@ -6048,6 +6939,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q44" s="55" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="55" t="inlineStr">
@@ -6116,6 +7008,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q45" s="55" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="55" t="inlineStr">
@@ -6184,6 +7077,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q46" s="55" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="55" t="inlineStr">
@@ -6252,6 +7146,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q47" s="55" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="55" t="inlineStr">
@@ -6318,6 +7213,11 @@
       <c r="P48" s="55" t="inlineStr">
         <is>
           <t>Тариф КТЖ (ж/д перевозки)</t>
+        </is>
+      </c>
+      <c r="Q48" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
         </is>
       </c>
     </row>
@@ -6388,6 +7288,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q49" s="55" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="55" t="inlineStr">
@@ -6456,6 +7357,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q50" s="55" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="55" t="inlineStr">
@@ -6524,6 +7426,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q51" s="55" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="55" t="inlineStr">
@@ -6592,6 +7495,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q52" s="55" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="55" t="inlineStr">
@@ -6660,6 +7564,11 @@
           <t>Связь и ИТ</t>
         </is>
       </c>
+      <c r="Q53" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Мобайл Телеком - Сервис"</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="55" t="inlineStr">
@@ -6728,6 +7637,11 @@
           <t>Маркетинг и представит.</t>
         </is>
       </c>
+      <c r="Q54" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Современные Печатные технологии "</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="55" t="inlineStr">
@@ -6796,6 +7710,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q55" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное Общество "Банк ЦентрКредит"</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="55" t="inlineStr">
@@ -6864,6 +7783,11 @@
           <t>Проф. услуги (бухг./юр./конс.)</t>
         </is>
       </c>
+      <c r="Q56" s="55" t="inlineStr">
+        <is>
+          <t>Индивидуальный предприниматель "Катрышева"</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="55" t="inlineStr">
@@ -6932,6 +7856,11 @@
           <t>Офис, аренда помещений, хоз.</t>
         </is>
       </c>
+      <c r="Q57" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "ALDAR EUROASIA PROPERTY MANAGEMENT"</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="55" t="inlineStr">
@@ -7000,6 +7929,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q58" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное Общество "Банк ЦентрКредит"</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="55" t="inlineStr">
@@ -7068,6 +8002,11 @@
           <t>Проф. услуги (бухг./юр./конс.)</t>
         </is>
       </c>
+      <c r="Q59" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное общество "Jusan Mobile"</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="55" t="inlineStr">
@@ -7136,6 +8075,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q60" s="55" t="inlineStr">
+        <is>
+          <t>Унбетпаев Ернар Байтасович</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="55" t="inlineStr">
@@ -7204,6 +8148,11 @@
           <t>Офис, аренда помещений, хоз.</t>
         </is>
       </c>
+      <c r="Q61" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "ALDAR EUROASIA PROPERTY MANAGEMENT"</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="55" t="inlineStr">
@@ -7272,6 +8221,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q62" s="55" t="inlineStr">
+        <is>
+          <t>Банк ЦентрКредит для ЗП</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="55" t="inlineStr">
@@ -7340,6 +8294,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q63" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "АВИАТУРАГЕНТСТВО ПАКС"</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="55" t="inlineStr">
@@ -7408,6 +8367,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q64" s="55" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="55" t="inlineStr">
@@ -7476,6 +8436,11 @@
           <t>Связь и ИТ</t>
         </is>
       </c>
+      <c r="Q65" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное общество "Транстелеком"</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="55" t="inlineStr">
@@ -7544,6 +8509,11 @@
           <t>Ремонт вагонов и узлов</t>
         </is>
       </c>
+      <c r="Q66" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "АФ АГМ-Табыс"</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="55" t="inlineStr">
@@ -7612,6 +8582,11 @@
           <t>Ремонт вагонов и узлов</t>
         </is>
       </c>
+      <c r="Q67" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Объединенное железнодорожное хозяйство"</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="55" t="inlineStr">
@@ -7680,6 +8655,11 @@
           <t>Ремонт вагонов и узлов</t>
         </is>
       </c>
+      <c r="Q68" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Нұр-Альфинур"</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="55" t="inlineStr">
@@ -7748,6 +8728,11 @@
           <t>Связь и ИТ</t>
         </is>
       </c>
+      <c r="Q69" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "LogiSoft" (ЛогиСофт)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="55" t="inlineStr">
@@ -7816,6 +8801,11 @@
           <t>Офис, аренда помещений, хоз.</t>
         </is>
       </c>
+      <c r="Q70" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "ALDAR EUROASIA PROPERTY MANAGEMENT"</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="55" t="inlineStr">
@@ -7884,6 +8874,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q71" s="55" t="inlineStr">
+        <is>
+          <t>Банк ЦентрКредит для ЗП</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="55" t="inlineStr">
@@ -7952,6 +8947,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q72" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="55" t="inlineStr">
@@ -8020,6 +9020,11 @@
           <t>Операторы вагонов (КТТ и др.)</t>
         </is>
       </c>
+      <c r="Q73" s="55" t="inlineStr">
+        <is>
+          <t>АО «КазТемирТранс» (КТТ)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="55" t="inlineStr">
@@ -8088,6 +9093,11 @@
           <t>Операторы вагонов (КТТ и др.)</t>
         </is>
       </c>
+      <c r="Q74" s="55" t="inlineStr">
+        <is>
+          <t>АО «КазТемирТранс» (КТТ)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="55" t="inlineStr">
@@ -8156,6 +9166,11 @@
           <t>Аренда/предоставление вагонов</t>
         </is>
       </c>
+      <c r="Q75" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "PetroComLogistics"</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="55" t="inlineStr">
@@ -8224,6 +9239,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q76" s="55" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="55" t="inlineStr">
@@ -8292,6 +9308,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q77" s="55" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="55" t="inlineStr">
@@ -8360,6 +9377,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q78" s="55" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="55" t="inlineStr">
@@ -8428,6 +9446,11 @@
           <t>Возврат средств</t>
         </is>
       </c>
+      <c r="Q79" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное общество "Фонд развития предприн</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="55" t="inlineStr">
@@ -8496,6 +9519,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q80" s="55" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="55" t="inlineStr">
@@ -8564,6 +9588,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q81" s="55" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="55" t="inlineStr">
@@ -8632,6 +9657,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q82" s="55" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="55" t="inlineStr">
@@ -8700,6 +9726,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q83" s="55" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="55" t="inlineStr">
@@ -8768,6 +9795,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q84" s="55" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="55" t="inlineStr">
@@ -8836,6 +9864,11 @@
           <t>Хоз. расходы и материалы</t>
         </is>
       </c>
+      <c r="Q85" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Office-Expert.kz"</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="55" t="inlineStr">
@@ -8904,6 +9937,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q86" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="55" t="inlineStr">
@@ -8972,6 +10010,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q87" s="55" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="55" t="inlineStr">
@@ -9040,6 +10079,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q88" s="55" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="55" t="inlineStr">
@@ -9108,6 +10148,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q89" s="55" t="inlineStr">
+        <is>
+          <t>ТОО EASY BOX</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="55" t="inlineStr">
@@ -9176,6 +10221,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q90" s="55" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="55" t="inlineStr">
@@ -9244,6 +10290,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q91" s="55" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="55" t="inlineStr">
@@ -9312,6 +10359,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q92" s="55" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="55" t="inlineStr">
@@ -9380,6 +10428,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q93" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное Общество "Банк ЦентрКредит"</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="55" t="inlineStr">
@@ -9448,6 +10501,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q94" s="55" t="inlineStr">
+        <is>
+          <t>Алим</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="55" t="inlineStr">
@@ -9516,6 +10574,11 @@
           <t>Проф. услуги (бухг./юр./конс.)</t>
         </is>
       </c>
+      <c r="Q95" s="55" t="inlineStr">
+        <is>
+          <t>Индивидуальный предприниматель "JOINMEDIA"</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="55" t="inlineStr">
@@ -9584,6 +10647,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q96" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="55" t="inlineStr">
@@ -9652,6 +10720,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q97" s="55" t="inlineStr">
+        <is>
+          <t>Банк ЦентрКредит для ЗП</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="55" t="inlineStr">
@@ -9720,6 +10793,11 @@
           <t>Прочие расходы</t>
         </is>
       </c>
+      <c r="Q98" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Рейл Транспортейшн"</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="55" t="inlineStr">
@@ -9788,6 +10866,11 @@
           <t>Аренда/предоставление вагонов</t>
         </is>
       </c>
+      <c r="Q99" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «InterLog Co»</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="55" t="inlineStr">
@@ -9856,6 +10939,11 @@
           <t>Прочие ж/д и ТЭУ услуги</t>
         </is>
       </c>
+      <c r="Q100" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "PRATA"</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="55" t="inlineStr">
@@ -9924,6 +11012,11 @@
           <t>Аренда/предоставление вагонов</t>
         </is>
       </c>
+      <c r="Q101" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "АРНА"</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="55" t="inlineStr">
@@ -9992,6 +11085,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q102" s="55" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="55" t="inlineStr">
@@ -10060,6 +11154,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q103" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="55" t="inlineStr">
@@ -10128,6 +11227,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q104" s="55" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="55" t="inlineStr">
@@ -10196,6 +11296,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q105" s="55" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="55" t="inlineStr">
@@ -10264,6 +11365,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q106" s="55" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="55" t="inlineStr">
@@ -10332,6 +11434,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q107" s="55" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="55" t="inlineStr">
@@ -10400,6 +11503,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q108" s="55" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="55" t="inlineStr">
@@ -10468,6 +11572,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q109" s="55" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="55" t="inlineStr">
@@ -10536,6 +11641,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q110" s="55" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="55" t="inlineStr">
@@ -10604,6 +11710,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q111" s="55" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="55" t="inlineStr">
@@ -10672,6 +11779,11 @@
           <t>Аренда/предоставление вагонов</t>
         </is>
       </c>
+      <c r="Q112" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Asia Railways Tracking Service (Азия Рэ</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="55" t="inlineStr">
@@ -10740,6 +11852,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q113" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="55" t="inlineStr">
@@ -10808,6 +11925,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q114" s="55" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="55" t="inlineStr">
@@ -10876,6 +11994,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q115" s="55" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="55" t="inlineStr">
@@ -10944,6 +12063,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q116" s="55" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="55" t="inlineStr">
@@ -11012,6 +12132,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q117" s="55" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="55" t="inlineStr">
@@ -11080,6 +12201,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q118" s="55" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="55" t="inlineStr">
@@ -11146,6 +12268,11 @@
       <c r="P119" s="55" t="inlineStr">
         <is>
           <t>Связь и ИТ</t>
+        </is>
+      </c>
+      <c r="Q119" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное Общество "Банк ЦентрКредит"</t>
         </is>
       </c>
     </row>
@@ -11216,6 +12343,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q120" s="55" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="55" t="inlineStr">
@@ -11284,6 +12412,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q121" s="55" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="55" t="inlineStr">
@@ -11352,6 +12481,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q122" s="55" t="inlineStr">
+        <is>
+          <t>Банк ЦентрКредит для ЗП</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="55" t="inlineStr">
@@ -11420,6 +12554,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q123" s="55" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="55" t="inlineStr">
@@ -11488,6 +12623,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q124" s="55" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="55" t="inlineStr">
@@ -11556,6 +12692,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q125" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="55" t="inlineStr">
@@ -11624,6 +12765,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q126" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="55" t="inlineStr">
@@ -11692,6 +12838,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q127" s="55" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="55" t="inlineStr">
@@ -11760,6 +12907,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q128" s="55" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="55" t="inlineStr">
@@ -11828,6 +12976,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q129" s="55" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="55" t="inlineStr">
@@ -11896,6 +13045,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q130" s="55" t="inlineStr">
+        <is>
+          <t>Белова Полина Сергеевна</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="55" t="inlineStr">
@@ -11964,6 +13118,11 @@
           <t>Хоз. расходы и материалы</t>
         </is>
       </c>
+      <c r="Q131" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Индивидуальный предприниматель "Ninety Plus </t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="55" t="inlineStr">
@@ -12032,6 +13191,11 @@
           <t>Аренда/предоставление вагонов</t>
         </is>
       </c>
+      <c r="Q132" s="55" t="inlineStr">
+        <is>
+          <t>филиал акционерного общества "Национальная к</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="55" t="inlineStr">
@@ -12100,6 +13264,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q133" s="55" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="55" t="inlineStr">
@@ -12168,6 +13333,11 @@
           <t>Аренда/предоставление вагонов</t>
         </is>
       </c>
+      <c r="Q134" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "ТОР Арыс"</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="55" t="inlineStr">
@@ -12236,6 +13406,11 @@
           <t>Ремонт вагонов и узлов</t>
         </is>
       </c>
+      <c r="Q135" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Нұр-Альфинур"</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="55" t="inlineStr">
@@ -12304,6 +13479,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q136" s="55" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="55" t="inlineStr">
@@ -12372,6 +13548,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q137" s="55" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="55" t="inlineStr">
@@ -12440,6 +13617,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q138" s="55" t="inlineStr">
+        <is>
+          <t>ТОО Rhenus Intermodal Systems</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="55" t="inlineStr">
@@ -12508,6 +13690,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q139" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «Atasu Global Trans»</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="55" t="inlineStr">
@@ -12576,6 +13763,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q140" s="55" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="55" t="inlineStr">
@@ -12644,6 +13832,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q141" s="55" t="inlineStr">
+        <is>
+          <t>Банк ЦентрКредит для ЗП</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="55" t="inlineStr">
@@ -12712,6 +13905,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q142" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Shiny river"</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="55" t="inlineStr">
@@ -12780,6 +13978,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q143" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="55" t="inlineStr">
@@ -12848,6 +14051,11 @@
           <t>Операторы вагонов (КТТ и др.)</t>
         </is>
       </c>
+      <c r="Q144" s="55" t="inlineStr">
+        <is>
+          <t>АО «КазТемирТранс» (КТТ)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="55" t="inlineStr">
@@ -12916,6 +14124,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q145" s="55" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="55" t="inlineStr">
@@ -12984,6 +14193,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q146" s="55" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="55" t="inlineStr">
@@ -13052,6 +14262,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q147" s="55" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="55" t="inlineStr">
@@ -13120,6 +14331,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q148" s="55" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="55" t="inlineStr">
@@ -13188,6 +14400,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q149" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное Общество "Банк ЦентрКредит"</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="55" t="inlineStr">
@@ -13256,6 +14473,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q150" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное общество "Банк "Bank RBK"</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="55" t="inlineStr">
@@ -13324,6 +14546,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q151" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное общество "Банк "Bank RBK"</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="55" t="inlineStr">
@@ -13392,6 +14619,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q152" s="55" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="55" t="inlineStr">
@@ -13460,6 +14688,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q153" s="55" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="55" t="inlineStr">
@@ -13528,6 +14757,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q154" s="55" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="55" t="inlineStr">
@@ -13596,6 +14826,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q155" s="55" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="55" t="inlineStr">
@@ -13664,6 +14895,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q156" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Максат-2030"</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="55" t="inlineStr">
@@ -13732,6 +14968,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q157" s="55" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="55" t="inlineStr">
@@ -13800,6 +15037,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q158" s="55" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="55" t="inlineStr">
@@ -13868,6 +15106,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q159" s="55" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="55" t="inlineStr">
@@ -13936,6 +15175,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q160" s="55" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="55" t="inlineStr">
@@ -14004,6 +15244,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q161" s="55" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="55" t="inlineStr">
@@ -14072,6 +15313,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q162" s="55" t="inlineStr">
+        <is>
+          <t>Банк ЦентрКредит для ЗП</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="55" t="inlineStr">
@@ -14140,6 +15386,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q163" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="55" t="inlineStr">
@@ -14208,6 +15459,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q164" s="55" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="55" t="inlineStr">
@@ -14276,6 +15528,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q165" s="55" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="55" t="inlineStr">
@@ -14344,6 +15597,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q166" s="55" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="55" t="inlineStr">
@@ -14412,6 +15666,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q167" s="55" t="inlineStr">
+        <is>
+          <t>ТОО Евразиан Каспиан Транс</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="55" t="inlineStr">
@@ -14480,6 +15739,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q168" s="55" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="55" t="inlineStr">
@@ -14548,6 +15808,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q169" s="55" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="55" t="inlineStr">
@@ -14616,6 +15877,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q170" s="55" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="55" t="inlineStr">
@@ -14682,6 +15944,11 @@
       <c r="P171" s="55" t="inlineStr">
         <is>
           <t>Тариф КТЖ (ж/д перевозки)</t>
+        </is>
+      </c>
+      <c r="Q171" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
         </is>
       </c>
     </row>
@@ -14752,6 +16019,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q172" s="55" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="55" t="inlineStr">
@@ -14820,6 +16088,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q173" s="55" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="55" t="inlineStr">
@@ -14888,6 +16157,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q174" s="55" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="55" t="inlineStr">
@@ -14956,6 +16226,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q175" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное Общество "Банк ЦентрКредит"</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="55" t="inlineStr">
@@ -15024,6 +16299,11 @@
           <t>Проф. услуги (бухг./юр./конс.)</t>
         </is>
       </c>
+      <c r="Q176" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "DV job"</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="55" t="inlineStr">
@@ -15092,6 +16372,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q177" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное Общество "Банк ЦентрКредит"</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="55" t="inlineStr">
@@ -15160,6 +16445,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q178" s="55" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="55" t="inlineStr">
@@ -15228,6 +16514,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q179" s="55" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="55" t="inlineStr">
@@ -15296,6 +16583,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q180" s="55" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="55" t="inlineStr">
@@ -15364,6 +16652,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q181" s="55" t="inlineStr">
+        <is>
+          <t>Данияр Алим</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="55" t="inlineStr">
@@ -15432,6 +16725,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q182" s="55" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="55" t="inlineStr">
@@ -15500,6 +16794,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q183" s="55" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="55" t="inlineStr">
@@ -15568,6 +16863,11 @@
           <t>Возврат выданных займов</t>
         </is>
       </c>
+      <c r="Q184" s="55" t="inlineStr">
+        <is>
+          <t>Серикбаев Адиль Даниярович</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="55" t="inlineStr">
@@ -15636,6 +16936,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q185" s="55" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="55" t="inlineStr">
@@ -15704,6 +17005,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q186" s="55" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="55" t="inlineStr">
@@ -15772,6 +17074,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q187" s="55" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="55" t="inlineStr">
@@ -15840,6 +17143,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q188" s="55" t="inlineStr">
+        <is>
+          <t>Аубакиров Алимбек Ерикович</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="55" t="inlineStr">
@@ -15908,6 +17216,11 @@
           <t>Ремонт вагонов и узлов</t>
         </is>
       </c>
+      <c r="Q189" s="55" t="inlineStr">
+        <is>
+          <t>Производственный кооператив "ИБРАЕВ+К"</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="55" t="inlineStr">
@@ -15976,6 +17289,11 @@
           <t>Аренда/предоставление вагонов</t>
         </is>
       </c>
+      <c r="Q190" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Asia Railways Tracking Service (Азия Рэ</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="55" t="inlineStr">
@@ -16044,6 +17362,11 @@
           <t>Прочие расходы</t>
         </is>
       </c>
+      <c r="Q191" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Kumo Trans"</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="55" t="inlineStr">
@@ -16112,6 +17435,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q192" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="55" t="inlineStr">
@@ -16180,6 +17508,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q193" s="55" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="55" t="inlineStr">
@@ -16246,6 +17575,11 @@
       <c r="P194" s="55" t="inlineStr">
         <is>
           <t>Тариф КТЖ (ж/д перевозки)</t>
+        </is>
+      </c>
+      <c r="Q194" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
         </is>
       </c>
     </row>
@@ -16316,6 +17650,11 @@
           <t>Возврат выданных займов</t>
         </is>
       </c>
+      <c r="Q195" s="55" t="inlineStr">
+        <is>
+          <t>Серикбаев Адиль Даниярович</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="55" t="inlineStr">
@@ -16384,6 +17723,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q196" s="55" t="inlineStr">
+        <is>
+          <t>ТОО Агро-Трейд-2030</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="55" t="inlineStr">
@@ -16452,6 +17796,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q197" s="55" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="55" t="inlineStr">
@@ -16520,6 +17865,11 @@
           <t>Связь и ИТ</t>
         </is>
       </c>
+      <c r="Q198" s="55" t="inlineStr">
+        <is>
+          <t>Индивидуальный предприниматель "Курасов С.Н.</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="55" t="inlineStr">
@@ -16588,6 +17938,11 @@
           <t>Связь и ИТ</t>
         </is>
       </c>
+      <c r="Q199" s="55" t="inlineStr">
+        <is>
+          <t>Индивидуальный предприниматель "Курасов С.Н.</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="55" t="inlineStr">
@@ -16656,6 +18011,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q200" s="55" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="55" t="inlineStr">
@@ -16724,6 +18080,11 @@
           <t>Спонсорство / благотвор.</t>
         </is>
       </c>
+      <c r="Q201" s="55" t="inlineStr">
+        <is>
+          <t>Пшебельский Богдан Евгеньевич</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="55" t="inlineStr">
@@ -16792,6 +18153,11 @@
           <t>Офис, аренда помещений, хоз.</t>
         </is>
       </c>
+      <c r="Q202" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "TOP.KZ (ТОП.КЗ)"</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="55" t="inlineStr">
@@ -16860,6 +18226,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q203" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное общество "Страховая компания "Ев</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="55" t="inlineStr">
@@ -16928,6 +18299,11 @@
           <t>Маркетинг и представит.</t>
         </is>
       </c>
+      <c r="Q204" s="55" t="inlineStr">
+        <is>
+          <t>Индивидуальный предприниматель "Makenzo medi</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="55" t="inlineStr">
@@ -16996,6 +18372,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q205" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="55" t="inlineStr">
@@ -17062,6 +18443,11 @@
       <c r="P206" s="55" t="inlineStr">
         <is>
           <t>Аренда/предоставление вагонов</t>
+        </is>
+      </c>
+      <c r="Q206" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "ЭРСАЛТ РЭЙЛ"</t>
         </is>
       </c>
     </row>
@@ -17132,6 +18518,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q207" s="55" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="55" t="inlineStr">
@@ -17200,6 +18587,11 @@
           <t>Возврат средств</t>
         </is>
       </c>
+      <c r="Q208" s="55" t="inlineStr">
+        <is>
+          <t>Филиал АО "Bereke Bank" (ДБ Lesha Bank LLC (</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="55" t="inlineStr">
@@ -17268,6 +18660,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q209" s="55" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="55" t="inlineStr">
@@ -17336,6 +18729,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q210" s="55" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="55" t="inlineStr">
@@ -17404,6 +18798,11 @@
           <t>Ремонт вагонов и узлов</t>
         </is>
       </c>
+      <c r="Q211" s="55" t="inlineStr">
+        <is>
+          <t>Производственный кооператив "ИБРАЕВ+К"</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="55" t="inlineStr">
@@ -17472,6 +18871,11 @@
           <t>Ремонт вагонов и узлов</t>
         </is>
       </c>
+      <c r="Q212" s="55" t="inlineStr">
+        <is>
+          <t>филиал акционерного общества "Национальная к</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="55" t="inlineStr">
@@ -17540,6 +18944,11 @@
           <t>Выданные займы (связ. лица)</t>
         </is>
       </c>
+      <c r="Q213" s="55" t="inlineStr">
+        <is>
+          <t>Серикбаев А.Д.</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="55" t="inlineStr">
@@ -17608,6 +19017,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q214" s="55" t="inlineStr">
+        <is>
+          <t>Банк ЦентрКредит для ЗП</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="55" t="inlineStr">
@@ -17676,6 +19090,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q215" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="55" t="inlineStr">
@@ -17744,6 +19163,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q216" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="55" t="inlineStr">
@@ -17812,6 +19236,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q217" s="55" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="55" t="inlineStr">
@@ -17880,6 +19305,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q218" s="55" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="55" t="inlineStr">
@@ -17948,6 +19374,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q219" s="55" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="55" t="inlineStr">
@@ -18016,6 +19443,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q220" s="55" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="55" t="inlineStr">
@@ -18084,6 +19512,11 @@
           <t>Налоги и отчисления</t>
         </is>
       </c>
+      <c r="Q221" s="55" t="inlineStr">
+        <is>
+          <t>УГД по Есильскому району ДГД по городу Астан</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="55" t="inlineStr">
@@ -18152,6 +19585,11 @@
           <t>Связь и ИТ</t>
         </is>
       </c>
+      <c r="Q222" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Рика"</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="55" t="inlineStr">
@@ -18220,6 +19658,11 @@
           <t>Ремонт вагонов и узлов</t>
         </is>
       </c>
+      <c r="Q223" s="55" t="inlineStr">
+        <is>
+          <t>Филиал акционерного общества «Национальная к</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="55" t="inlineStr">
@@ -18288,6 +19731,11 @@
           <t>Налоги и отчисления</t>
         </is>
       </c>
+      <c r="Q224" s="55" t="inlineStr">
+        <is>
+          <t>НАО "Государственная корпорация "Правительст</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="55" t="inlineStr">
@@ -18356,6 +19804,11 @@
           <t>Выданные займы (связ. лица)</t>
         </is>
       </c>
+      <c r="Q225" s="55" t="inlineStr">
+        <is>
+          <t>Серикбаев А.Д.</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="55" t="inlineStr">
@@ -18424,6 +19877,11 @@
           <t>Налоги и отчисления</t>
         </is>
       </c>
+      <c r="Q226" s="55" t="inlineStr">
+        <is>
+          <t>НАО "Государственная корпорация "Правительст</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="55" t="inlineStr">
@@ -18492,6 +19950,11 @@
           <t>Налоги и отчисления</t>
         </is>
       </c>
+      <c r="Q227" s="55" t="inlineStr">
+        <is>
+          <t>НАО "Государственная корпорация "Правительст</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="55" t="inlineStr">
@@ -18560,6 +20023,11 @@
           <t>Налоги и отчисления</t>
         </is>
       </c>
+      <c r="Q228" s="55" t="inlineStr">
+        <is>
+          <t>НАО "Государственная корпорация "Правительст</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="55" t="inlineStr">
@@ -18628,6 +20096,11 @@
           <t>Налоги и отчисления</t>
         </is>
       </c>
+      <c r="Q229" s="55" t="inlineStr">
+        <is>
+          <t>УГД по Есильскому району ДГД по городу Астан</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="55" t="inlineStr">
@@ -18696,6 +20169,11 @@
           <t>Налоги и отчисления</t>
         </is>
       </c>
+      <c r="Q230" s="55" t="inlineStr">
+        <is>
+          <t>УГД по Есильскому району ДГД по городу Астан</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="55" t="inlineStr">
@@ -18764,6 +20242,11 @@
           <t>Налоги и отчисления</t>
         </is>
       </c>
+      <c r="Q231" s="55" t="inlineStr">
+        <is>
+          <t>УГД по Есильскому району ДГД по городу Астан</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="55" t="inlineStr">
@@ -18832,6 +20315,11 @@
           <t>Налоги и отчисления</t>
         </is>
       </c>
+      <c r="Q232" s="55" t="inlineStr">
+        <is>
+          <t>НАО "Государственная корпорация "Правительст</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="55" t="inlineStr">
@@ -18900,6 +20388,11 @@
           <t>Аренда/предоставление вагонов</t>
         </is>
       </c>
+      <c r="Q233" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "USM-Logistics"</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="55" t="inlineStr">
@@ -18966,6 +20459,11 @@
       <c r="P234" s="55" t="inlineStr">
         <is>
           <t>Тариф КТЖ (ж/д перевозки)</t>
+        </is>
+      </c>
+      <c r="Q234" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
         </is>
       </c>
     </row>
@@ -19036,6 +20534,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q235" s="55" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="55" t="inlineStr">
@@ -19104,6 +20603,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q236" s="55" t="inlineStr">
+        <is>
+          <t>ТОВАРИЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="55" t="inlineStr">
@@ -19172,6 +20676,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q237" s="55" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="55" t="inlineStr">
@@ -19240,6 +20745,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q238" s="55" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="55" t="inlineStr">
@@ -19308,6 +20814,11 @@
           <t>Выданные займы (связ. лица)</t>
         </is>
       </c>
+      <c r="Q239" s="55" t="inlineStr">
+        <is>
+          <t>Серикбаев А.Д.</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="55" t="inlineStr">
@@ -19376,6 +20887,11 @@
           <t>Выданные займы (связ. лица)</t>
         </is>
       </c>
+      <c r="Q240" s="55" t="inlineStr">
+        <is>
+          <t>Серикбаев А.Д.</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="55" t="inlineStr">
@@ -19444,6 +20960,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q241" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="55" t="inlineStr">
@@ -19512,6 +21033,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q242" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="55" t="inlineStr">
@@ -19580,6 +21106,11 @@
           <t>Офис, аренда помещений, хоз.</t>
         </is>
       </c>
+      <c r="Q243" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "AquaPoint Qazaqstan"</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="55" t="inlineStr">
@@ -19648,6 +21179,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q244" s="55" t="inlineStr">
+        <is>
+          <t>Аубакиров Алимбек Ерикович</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="55" t="inlineStr">
@@ -19716,6 +21252,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q245" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное общество "Банк "Bank RBK"</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="55" t="inlineStr">
@@ -19782,6 +21323,11 @@
       <c r="P246" s="55" t="inlineStr">
         <is>
           <t>Тариф КТЖ (ж/д перевозки)</t>
+        </is>
+      </c>
+      <c r="Q246" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
         </is>
       </c>
     </row>
@@ -19852,6 +21398,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q247" s="55" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="55" t="inlineStr">
@@ -19920,6 +21467,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q248" s="55" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="55" t="inlineStr">
@@ -19988,6 +21536,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q249" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное Общество "Банк ЦентрКредит"</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="55" t="inlineStr">
@@ -20056,6 +21609,11 @@
           <t>Проф. услуги (бухг./юр./конс.)</t>
         </is>
       </c>
+      <c r="Q250" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Digital Sales Consulting"</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="55" t="inlineStr">
@@ -20124,6 +21682,11 @@
           <t>Ремонт вагонов и узлов</t>
         </is>
       </c>
+      <c r="Q251" s="55" t="inlineStr">
+        <is>
+          <t>филиал акционерного общества "Национальная к</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="55" t="inlineStr">
@@ -20192,6 +21755,11 @@
           <t>Ремонт вагонов и узлов</t>
         </is>
       </c>
+      <c r="Q252" s="55" t="inlineStr">
+        <is>
+          <t>филиал акционерного общества "Национальная к</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="55" t="inlineStr">
@@ -20260,6 +21828,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q253" s="55" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="55" t="inlineStr">
@@ -20328,6 +21897,11 @@
           <t>Ремонт вагонов и узлов</t>
         </is>
       </c>
+      <c r="Q254" s="55" t="inlineStr">
+        <is>
+          <t>ТОО ""SK RAILWAY Service""</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="55" t="inlineStr">
@@ -20396,6 +21970,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q255" s="55" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="55" t="inlineStr">
@@ -20464,6 +22039,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q256" s="55" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="55" t="inlineStr">
@@ -20532,6 +22108,11 @@
           <t>Прочие ж/д и ТЭУ услуги</t>
         </is>
       </c>
+      <c r="Q257" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "ЭДЕМ ТРАНС"</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="55" t="inlineStr">
@@ -20600,6 +22181,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q258" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="55" t="inlineStr">
@@ -20668,6 +22254,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q259" s="55" t="inlineStr">
+        <is>
+          <t>АО "Банк ЦентрКредит"</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="55" t="inlineStr">
@@ -20736,6 +22327,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q260" s="55" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="55" t="inlineStr">
@@ -20802,6 +22394,11 @@
       <c r="P261" s="55" t="inlineStr">
         <is>
           <t>Зарплата</t>
+        </is>
+      </c>
+      <c r="Q261" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное общество "Банк "Bank RBK"</t>
         </is>
       </c>
     </row>
@@ -20868,6 +22465,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q262" s="55" t="inlineStr">
+        <is>
+          <t>АО "Банк ЦентрКредит"</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="55" t="inlineStr">
@@ -20936,6 +22538,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q263" s="55" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="55" t="inlineStr">
@@ -21002,6 +22605,11 @@
       <c r="P264" s="55" t="inlineStr">
         <is>
           <t>Выданные займы (связ. лица)</t>
+        </is>
+      </c>
+      <c r="Q264" s="55" t="inlineStr">
+        <is>
+          <t>Серикбаев А.Д.</t>
         </is>
       </c>
     </row>
@@ -21072,6 +22680,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q265" s="55" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="55" t="inlineStr">
@@ -21140,6 +22749,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q266" s="55" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="55" t="inlineStr">
@@ -21208,6 +22818,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q267" s="55" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="55" t="inlineStr">
@@ -21276,6 +22887,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q268" s="55" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="55" t="inlineStr">
@@ -21344,6 +22956,11 @@
           <t>Прочие расходы</t>
         </is>
       </c>
+      <c r="Q269" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "ALDAR EUROASIA PROPERTY MANAGEMENT"</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="55" t="inlineStr">
@@ -21412,6 +23029,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q270" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное Общество "Банк ЦентрКредит"</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="55" t="inlineStr">
@@ -21480,6 +23102,11 @@
           <t>Ремонт вагонов и узлов</t>
         </is>
       </c>
+      <c r="Q271" s="55" t="inlineStr">
+        <is>
+          <t>филиал акционерного общества "Национальная к</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="55" t="inlineStr">
@@ -21548,6 +23175,11 @@
           <t>Прочие расходы</t>
         </is>
       </c>
+      <c r="Q272" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "ALDAR EUROASIA PROPERTY MANAGEMENT"</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="55" t="inlineStr">
@@ -21616,6 +23248,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q273" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное Общество "Банк ЦентрКредит"</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="55" t="inlineStr">
@@ -21684,6 +23321,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q274" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "АВИАТУРАГЕНТСТВО ПАКС"</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="55" t="inlineStr">
@@ -21752,6 +23394,11 @@
           <t>Страхование</t>
         </is>
       </c>
+      <c r="Q275" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "АВИАТУРАГЕНТСТВО ПАКС"</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="55" t="inlineStr">
@@ -21820,6 +23467,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q276" s="55" t="inlineStr">
+        <is>
+          <t>ТАШМЕТОВ САКЕН КУАНЫШЕВИЧ</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="55" t="inlineStr">
@@ -21888,6 +23540,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q277" s="55" t="inlineStr">
+        <is>
+          <t>Белова Полина Сергеевна</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="55" t="inlineStr">
@@ -21956,6 +23613,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q278" s="55" t="inlineStr">
+        <is>
+          <t>Доолоткулов Данияр Дулатбекович</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="55" t="inlineStr">
@@ -22024,6 +23686,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q279" s="55" t="inlineStr">
+        <is>
+          <t>Жунусова Камила Жигитовна</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="55" t="inlineStr">
@@ -22092,6 +23759,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q280" s="55" t="inlineStr">
+        <is>
+          <t>Байльденова Шолпан Болатовна</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="55" t="inlineStr">
@@ -22160,6 +23832,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q281" s="55" t="inlineStr">
+        <is>
+          <t>Сибагатов Хамардин Смагулович</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="55" t="inlineStr">
@@ -22228,6 +23905,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q282" s="55" t="inlineStr">
+        <is>
+          <t>Сейтқадыр Дарын Нұрсейтұлы</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="55" t="inlineStr">
@@ -22296,6 +23978,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q283" s="55" t="inlineStr">
+        <is>
+          <t>Ашимов Арсен Беклербекович</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="55" t="inlineStr">
@@ -22364,6 +24051,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q284" s="55" t="inlineStr">
+        <is>
+          <t>Таджимурадова Асем Казыевна</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="55" t="inlineStr">
@@ -22432,6 +24124,11 @@
           <t>Связь и ИТ</t>
         </is>
       </c>
+      <c r="Q285" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Белый Ветер KZ"</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="55" t="inlineStr">
@@ -22500,6 +24197,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q286" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное Общество "Банк ЦентрКредит"</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="55" t="inlineStr">
@@ -22568,6 +24270,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q287" s="55" t="inlineStr">
+        <is>
+          <t>Серикбаев А.Д.</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="55" t="inlineStr">
@@ -22636,6 +24343,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q288" s="55" t="inlineStr">
+        <is>
+          <t>Унбетпаев Ернар Байтасович</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="55" t="inlineStr">
@@ -22704,6 +24416,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q289" s="55" t="inlineStr">
+        <is>
+          <t>Алим</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="55" t="inlineStr">
@@ -22772,6 +24489,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q290" s="55" t="inlineStr">
+        <is>
+          <t>Аубакиров Алимбек Ерикович</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="55" t="inlineStr">
@@ -22840,6 +24562,11 @@
           <t>Прочие расходы</t>
         </is>
       </c>
+      <c r="Q291" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "ALDAR EUROASIA PROPERTY MANAGEMENT"</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="55" t="inlineStr">
@@ -22908,6 +24635,11 @@
           <t>Проф. услуги (бухг./юр./конс.)</t>
         </is>
       </c>
+      <c r="Q292" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "АВИАТУРАГЕНТСТВО ПАКС"</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="55" t="inlineStr">
@@ -22976,6 +24708,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q293" s="55" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="55" t="inlineStr">
@@ -23044,6 +24777,11 @@
           <t>Аренда/предоставление вагонов</t>
         </is>
       </c>
+      <c r="Q294" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Asia Railways Tracking Service (Азия Рэ</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="55" t="inlineStr">
@@ -23112,6 +24850,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q295" s="55" t="inlineStr">
+        <is>
+          <t>Банк ЦентрКредит для ЗП</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="55" t="inlineStr">
@@ -23180,6 +24923,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q296" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "АВИАТУРАГЕНТСТВО ПАКС"</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="55" t="inlineStr">
@@ -23248,6 +24996,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q297" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "АВИАТУРАГЕНТСТВО ПАКС"</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="55" t="inlineStr">
@@ -23316,6 +25069,11 @@
           <t>Проф. услуги (бухг./юр./конс.)</t>
         </is>
       </c>
+      <c r="Q298" s="55" t="inlineStr">
+        <is>
+          <t>Индивидуальный предприниматель "ON TIME ACCO</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="55" t="inlineStr">
@@ -23384,6 +25142,11 @@
           <t>Проф. услуги (бухг./юр./конс.)</t>
         </is>
       </c>
+      <c r="Q299" s="55" t="inlineStr">
+        <is>
+          <t>Индивидуальный предприниматель "JOINMEDIA"</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="55" t="inlineStr">
@@ -23452,6 +25215,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q300" s="55" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="55" t="inlineStr">
@@ -23520,6 +25284,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q301" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "АВИАТУРАГЕНТСТВО ПАКС"</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="55" t="inlineStr">
@@ -23588,6 +25357,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q302" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное общество "Банк "Bank RBK"</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="55" t="inlineStr">
@@ -23656,6 +25430,11 @@
           <t>Офис, аренда помещений, хоз.</t>
         </is>
       </c>
+      <c r="Q303" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "ALDAR EUROASIA PROPERTY MANAGEMENT"</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="55" t="inlineStr">
@@ -23724,6 +25503,11 @@
           <t>Финансовый лизинг</t>
         </is>
       </c>
+      <c r="Q304" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Арлан Лизинг"</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="55" t="inlineStr">
@@ -23792,6 +25576,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q305" s="55" t="inlineStr">
+        <is>
+          <t>Банк ЦентрКредит для ЗП</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="55" t="inlineStr">
@@ -23860,6 +25649,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q306" s="55" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="55" t="inlineStr">
@@ -23928,6 +25718,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q307" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="55" t="inlineStr">
@@ -23996,6 +25791,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q308" s="55" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="55" t="inlineStr">
@@ -24064,6 +25860,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q309" s="55" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="55" t="inlineStr">
@@ -24132,6 +25929,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q310" s="55" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="55" t="inlineStr">
@@ -24200,6 +25998,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q311" s="55" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="55" t="inlineStr">
@@ -24268,6 +26067,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q312" s="55" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="55" t="inlineStr">
@@ -24336,6 +26136,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q313" s="55" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="55" t="inlineStr">
@@ -24404,6 +26205,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q314" s="55" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="55" t="inlineStr">
@@ -24472,6 +26274,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q315" s="55" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="55" t="inlineStr">
@@ -24540,6 +26343,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q316" s="55" t="inlineStr">
+        <is>
+          <t>Акционерное Общество "Банк ЦентрКредит"</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="55" t="inlineStr">
@@ -24608,6 +26416,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q317" s="55" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="55" t="inlineStr">
@@ -24676,6 +26485,11 @@
           <t>Тариф КТЖ (ж/д перевозки)</t>
         </is>
       </c>
+      <c r="Q318" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «КТЖ-Грузовые перевозки»</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="55" t="inlineStr">
@@ -24744,6 +26558,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q319" s="55" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="55" t="inlineStr">
@@ -24812,6 +26627,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q320" s="55" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="55" t="inlineStr">
@@ -24880,6 +26696,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q321" s="55" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="55" t="inlineStr">
@@ -24948,6 +26765,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q322" s="55" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="55" t="inlineStr">
@@ -25016,6 +26834,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q323" s="55" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="55" t="inlineStr">
@@ -25080,6 +26899,11 @@
           <t>Зарубежные перевозчики/экспедиторы</t>
         </is>
       </c>
+      <c r="Q324" s="55" t="inlineStr">
+        <is>
+          <t>MEGA STOCK CO. LTD (Таиланд)</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="55" t="inlineStr">
@@ -25148,6 +26972,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q325" s="55" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="55" t="inlineStr">
@@ -25212,6 +27037,11 @@
           <t>Зарубежные перевозчики/экспедиторы</t>
         </is>
       </c>
+      <c r="Q326" s="55" t="inlineStr">
+        <is>
+          <t>LLC Altyn Trans (Узб.)</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="55" t="inlineStr">
@@ -25280,6 +27110,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q327" s="55" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="55" t="inlineStr">
@@ -25344,6 +27175,11 @@
           <t>Зарубежные перевозчики/экспедиторы</t>
         </is>
       </c>
+      <c r="Q328" s="55" t="inlineStr">
+        <is>
+          <t>MEGA STOCK CO. LTD (Таиланд)</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="55" t="inlineStr">
@@ -25412,6 +27248,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q329" s="55" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="55" t="inlineStr">
@@ -25476,6 +27313,11 @@
           <t>Зарубежные перевозчики/экспедиторы</t>
         </is>
       </c>
+      <c r="Q330" s="55" t="inlineStr">
+        <is>
+          <t>MEGA STOCK CO. LTD (Таиланд)</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="55" t="inlineStr">
@@ -25544,6 +27386,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q331" s="55" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="55" t="inlineStr">
@@ -25608,6 +27451,11 @@
           <t>Зарубежные перевозчики/экспедиторы</t>
         </is>
       </c>
+      <c r="Q332" s="55" t="inlineStr">
+        <is>
+          <t>Turkmen Demiryol Express (Туркм.)</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="55" t="inlineStr">
@@ -25676,6 +27524,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q333" s="55" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="55" t="inlineStr">
@@ -25740,6 +27589,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q334" s="55" t="inlineStr">
+        <is>
+          <t>LLC Sadko International (Узб.)</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="55" t="inlineStr">
@@ -25804,6 +27658,11 @@
           <t>Зарубежные перевозчики/экспедиторы</t>
         </is>
       </c>
+      <c r="Q335" s="55" t="inlineStr">
+        <is>
+          <t>MEGA STOCK CO. LTD (Таиланд)</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="55" t="inlineStr">
@@ -25872,6 +27731,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q336" s="55" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="55" t="inlineStr">
@@ -25940,6 +27800,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q337" s="55" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="55" t="inlineStr">
@@ -26004,6 +27865,11 @@
           <t>Командировки и подотчёт</t>
         </is>
       </c>
+      <c r="Q338" s="55" t="inlineStr">
+        <is>
+          <t>LLC Sadko International (Узб.)</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="55" t="inlineStr">
@@ -26072,6 +27938,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q339" s="55" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="55" t="inlineStr">
@@ -26136,6 +28003,11 @@
           <t>Зарубежные перевозчики/экспедиторы</t>
         </is>
       </c>
+      <c r="Q340" s="55" t="inlineStr">
+        <is>
+          <t>ООО «ТрансАльянс Запад» (РФ)</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="55" t="inlineStr">
@@ -26204,6 +28076,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q341" s="55" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="55" t="inlineStr">
@@ -26268,6 +28141,11 @@
           <t>Зарубежные перевозчики/экспедиторы</t>
         </is>
       </c>
+      <c r="Q342" s="55" t="inlineStr">
+        <is>
+          <t>ООО «ТрансАльянс Запад» (РФ)</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="55" t="inlineStr">
@@ -26336,6 +28214,7 @@
           <t>Покупка/продажа валюты</t>
         </is>
       </c>
+      <c r="Q343" s="55" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="55" t="inlineStr">
@@ -26400,6 +28279,11 @@
           <t>Проценты по депозиту</t>
         </is>
       </c>
+      <c r="Q344" s="55" t="inlineStr">
+        <is>
+          <t>АО "Банк "Bank RBK"</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="55" t="inlineStr">
@@ -26464,6 +28348,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q345" s="55" t="inlineStr">
+        <is>
+          <t>ТОО Kaz-Smart Logistics</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="55" t="inlineStr">
@@ -26528,6 +28417,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q346" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "AsstrА Almaty" (АсстрА Алматы)</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="55" t="inlineStr">
@@ -26592,6 +28486,11 @@
           <t>Проценты по депозиту</t>
         </is>
       </c>
+      <c r="Q347" s="55" t="inlineStr">
+        <is>
+          <t>АО "Банк "Bank RBK"</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="55" t="inlineStr">
@@ -26656,6 +28555,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q348" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «Altyn Shyghys»</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="55" t="inlineStr">
@@ -26720,6 +28624,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q349" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «Altyn Shyghys»</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="55" t="inlineStr">
@@ -26784,6 +28693,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q350" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "Экспорт-М"</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="55" t="inlineStr">
@@ -26848,6 +28762,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q351" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «QAZAQ-ASTYQ GROUP»</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="55" t="inlineStr">
@@ -26912,6 +28831,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q352" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «QAZAQ-ASTYQ GROUP»</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="55" t="inlineStr">
@@ -26976,6 +28900,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q353" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="55" t="inlineStr">
@@ -27040,6 +28969,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q354" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="55" t="inlineStr">
@@ -27104,6 +29038,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q355" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="55" t="inlineStr">
@@ -27168,6 +29107,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q356" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="55" t="inlineStr">
@@ -27232,6 +29176,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q357" s="55" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="55" t="inlineStr">
@@ -27296,6 +29241,11 @@
           <t>Зарплата</t>
         </is>
       </c>
+      <c r="Q358" s="55" t="inlineStr">
+        <is>
+          <t>АО "Банк "Bank RBK"</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="55" t="inlineStr">
@@ -27360,6 +29310,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q359" s="55" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="55" t="inlineStr">
@@ -27424,6 +29375,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q360" s="55" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="55" t="inlineStr">
@@ -27488,6 +29440,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q361" s="55" t="inlineStr">
+        <is>
+          <t>ТОО ROYAL EXPORT</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="55" t="inlineStr">
@@ -27552,6 +29509,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q362" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «Altyn Shyghys»</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="55" t="inlineStr">
@@ -27616,6 +29578,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q363" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «QAZAQ-ASTYQ GROUP»</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="55" t="inlineStr">
@@ -27680,6 +29647,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q364" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="55" t="inlineStr">
@@ -27744,6 +29716,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q365" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="55" t="inlineStr">
@@ -27808,6 +29785,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q366" s="55" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="55" t="inlineStr">
@@ -27872,6 +29850,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q367" s="55" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="55" t="inlineStr">
@@ -27936,6 +29915,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q368" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «QAZAQ-ASTYQ GROUP»</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="55" t="inlineStr">
@@ -28000,6 +29984,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q369" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="55" t="inlineStr">
@@ -28064,6 +30053,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q370" s="55" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="55" t="inlineStr">
@@ -28128,6 +30118,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q371" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «QAZAQ-ASTYQ GROUP»</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="55" t="inlineStr">
@@ -28192,6 +30187,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q372" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="55" t="inlineStr">
@@ -28256,6 +30256,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q373" s="55" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="55" t="inlineStr">
@@ -28320,6 +30321,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q374" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "TimeAgro"</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="55" t="inlineStr">
@@ -28384,6 +30390,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q375" s="55" t="inlineStr">
+        <is>
+          <t>ТОО ROYAL EXPORT</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="55" t="inlineStr">
@@ -28448,6 +30459,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q376" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="55" t="inlineStr">
@@ -28512,6 +30528,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q377" s="55" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="55" t="inlineStr">
@@ -28576,6 +30593,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q378" s="55" t="inlineStr">
+        <is>
+          <t>ТОО Каз Алтын Групп</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="55" t="inlineStr">
@@ -28640,6 +30662,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q379" s="55" t="inlineStr">
+        <is>
+          <t>ТОО East Agro Company</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="55" t="inlineStr">
@@ -28704,6 +30731,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q380" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «Altyn Shyghys»</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="55" t="inlineStr">
@@ -28768,6 +30800,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q381" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="55" t="inlineStr">
@@ -28832,6 +30869,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q382" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="55" t="inlineStr">
@@ -28896,6 +30938,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q383" s="55" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="55" t="inlineStr">
@@ -28958,6 +31001,11 @@
       <c r="P384" s="55" t="inlineStr">
         <is>
           <t>Банковские комиссии</t>
+        </is>
+      </c>
+      <c r="Q384" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
         </is>
       </c>
     </row>
@@ -29024,6 +31072,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q385" s="55" t="inlineStr">
+        <is>
+          <t>ТОО Темир Экспресс Логистик</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="55" t="inlineStr">
@@ -29088,6 +31141,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q386" s="55" t="inlineStr">
+        <is>
+          <t>ТОО REGAL EXPORT</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="55" t="inlineStr">
@@ -29152,6 +31210,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q387" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="55" t="inlineStr">
@@ -29216,6 +31279,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q388" s="55" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="55" t="inlineStr">
@@ -29280,6 +31344,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q389" s="55" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="55" t="inlineStr">
@@ -29344,6 +31409,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q390" s="55" t="inlineStr">
+        <is>
+          <t>ТОО ROYAL EXPORT</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="55" t="inlineStr">
@@ -29408,6 +31478,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q391" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="55" t="inlineStr">
@@ -29472,6 +31547,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q392" s="55" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="55" t="inlineStr">
@@ -29536,6 +31612,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q393" s="55" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="55" t="inlineStr">
@@ -29600,6 +31677,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q394" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "TimeAgro"</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="55" t="inlineStr">
@@ -29664,6 +31746,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q395" s="55" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="55" t="inlineStr">
@@ -29728,6 +31811,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q396" s="55" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="55" t="inlineStr">
@@ -29792,6 +31876,11 @@
           <t>Проценты по кредиту</t>
         </is>
       </c>
+      <c r="Q397" s="55" t="inlineStr">
+        <is>
+          <t>АО "Банк "Bank RBK"</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="55" t="inlineStr">
@@ -29856,6 +31945,11 @@
           <t>Проценты по кредиту</t>
         </is>
       </c>
+      <c r="Q398" s="55" t="inlineStr">
+        <is>
+          <t>АО "Банк "Bank RBK"</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="55" t="inlineStr">
@@ -29920,6 +32014,11 @@
           <t>Проценты по кредиту</t>
         </is>
       </c>
+      <c r="Q399" s="55" t="inlineStr">
+        <is>
+          <t>АО "Банк "Bank RBK"</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="55" t="inlineStr">
@@ -29984,6 +32083,11 @@
           <t>Проценты по кредиту</t>
         </is>
       </c>
+      <c r="Q400" s="55" t="inlineStr">
+        <is>
+          <t>АО "Банк "Bank RBK"</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="55" t="inlineStr">
@@ -30048,6 +32152,11 @@
           <t>Проценты по кредиту</t>
         </is>
       </c>
+      <c r="Q401" s="55" t="inlineStr">
+        <is>
+          <t>АО "Банк "Bank RBK"</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="55" t="inlineStr">
@@ -30112,6 +32221,11 @@
           <t>Проценты по кредиту</t>
         </is>
       </c>
+      <c r="Q402" s="55" t="inlineStr">
+        <is>
+          <t>АО "Банк "Bank RBK"</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="55" t="inlineStr">
@@ -30176,6 +32290,11 @@
           <t>Проценты по кредиту</t>
         </is>
       </c>
+      <c r="Q403" s="55" t="inlineStr">
+        <is>
+          <t>АО "Банк "Bank RBK"</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="55" t="inlineStr">
@@ -30238,6 +32357,11 @@
       <c r="P404" s="55" t="inlineStr">
         <is>
           <t>Погашение кредита — тело</t>
+        </is>
+      </c>
+      <c r="Q404" s="55" t="inlineStr">
+        <is>
+          <t>АО "Банк "Bank RBK"</t>
         </is>
       </c>
     </row>
@@ -30304,6 +32428,11 @@
           <t>Возврат выданных займов</t>
         </is>
       </c>
+      <c r="Q405" s="55" t="inlineStr">
+        <is>
+          <t>Данияр Алим</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="55" t="inlineStr">
@@ -30368,6 +32497,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q406" s="55" t="inlineStr">
+        <is>
+          <t>ТОО ALTAI MAI</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="55" t="inlineStr">
@@ -30432,6 +32566,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q407" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "ШыгысАгроТорг"</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="55" t="inlineStr">
@@ -30496,6 +32635,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q408" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="55" t="inlineStr">
@@ -30560,6 +32704,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q409" s="55" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="55" t="inlineStr">
@@ -30624,6 +32769,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q410" s="55" t="inlineStr">
+        <is>
+          <t>ТОО «Altyn Shyghys»</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="55" t="inlineStr">
@@ -30688,6 +32838,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q411" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="55" t="inlineStr">
@@ -30752,6 +32907,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q412" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="55" t="inlineStr">
@@ -30816,6 +32976,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q413" s="55" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="55" t="inlineStr">
@@ -30880,6 +33041,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q414" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="55" t="inlineStr">
@@ -30944,6 +33110,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q415" s="55" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="55" t="inlineStr">
@@ -31008,6 +33175,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q416" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "УСТЬ-КАМЕНОГОРСКИЙ МАСЛО-ЭКСТРАКЦИОННЫЙ</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="55" t="inlineStr">
@@ -31072,6 +33244,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q417" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="55" t="inlineStr">
@@ -31136,6 +33313,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q418" s="55" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="55" t="inlineStr">
@@ -31200,6 +33378,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q419" s="55" t="inlineStr">
+        <is>
+          <t>ТОО ROYAL EXPORT</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="55" t="inlineStr">
@@ -31264,6 +33447,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q420" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="55" t="inlineStr">
@@ -31328,6 +33516,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q421" s="55" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="55" t="inlineStr">
@@ -31392,6 +33581,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q422" s="55" t="inlineStr">
+        <is>
+          <t>ТОО Каз Алтын Групп</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="55" t="inlineStr">
@@ -31454,6 +33648,11 @@
       <c r="P423" s="55" t="inlineStr">
         <is>
           <t>Прочие расходы</t>
+        </is>
+      </c>
+      <c r="Q423" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
         </is>
       </c>
     </row>
@@ -31520,6 +33719,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q424" s="55" t="inlineStr">
+        <is>
+          <t>ТОО Kaz-Smart Logistics</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="55" t="inlineStr">
@@ -31584,6 +33788,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q425" s="55" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="55" t="inlineStr">
@@ -31648,6 +33853,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q426" s="55" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="55" t="inlineStr">
@@ -31712,6 +33918,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q427" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="55" t="inlineStr">
@@ -31776,6 +33987,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q428" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="55" t="inlineStr">
@@ -31840,6 +34056,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q429" s="55" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="55" t="inlineStr">
@@ -31904,6 +34121,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q430" s="55" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="55" t="inlineStr">
@@ -31968,6 +34186,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q431" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "FRS logistics"</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="55" t="inlineStr">
@@ -32032,6 +34255,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q432" s="55" t="inlineStr">
+        <is>
+          <t>ТОО ROYAL EXPORT</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="55" t="inlineStr">
@@ -32096,6 +34324,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q433" s="55" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="55" t="inlineStr">
@@ -32160,6 +34389,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q434" s="55" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="55" t="inlineStr">
@@ -32224,6 +34454,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q435" s="55" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="55" t="inlineStr">
@@ -32288,6 +34519,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q436" s="55" t="inlineStr">
+        <is>
+          <t>ТОО "GREENLIGHTS (ГРИНЛАЙТС)"</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="55" t="inlineStr">
@@ -32352,6 +34588,11 @@
           <t>Банковские комиссии</t>
         </is>
       </c>
+      <c r="Q437" s="55" t="inlineStr">
+        <is>
+          <t>ФИЛИАЛ АО "BANK RBK" В Г.АСТАНА</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="55" t="inlineStr">
@@ -32416,6 +34657,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q438" s="55" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="55" t="inlineStr">
@@ -32482,6 +34724,11 @@
           <t>Операционная выручка (ТЭО, вагоны)</t>
         </is>
       </c>
+      <c r="Q439" s="55" t="inlineStr">
+        <is>
+          <t>ALBATAREEQ TRADING LLC (ОАЭ)</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="55" t="inlineStr">
@@ -32546,6 +34793,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q440" s="55" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="55" t="inlineStr">
@@ -32610,6 +34858,7 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q441" s="55" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="55" t="inlineStr">
@@ -32674,12 +34923,13 @@
           <t>Перевод между своими счетами</t>
         </is>
       </c>
+      <c r="Q442" s="55" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P442"/>
+  <autoFilter ref="A4:Q442"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/waystar-management-report/WayStar_Управленка_Июль2026.xlsx
+++ b/waystar-management-report/WayStar_Управленка_Июль2026.xlsx
@@ -880,12 +880,12 @@
       </c>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="8">
-        <f>'ОПиУ'!C13</f>
+        <f>'ОПиУ'!C14</f>
         <v/>
       </c>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="8">
-        <f>'ОПиУ'!C26</f>
+        <f>'ОПиУ'!C25</f>
         <v/>
       </c>
       <c r="F6" s="7" t="n"/>
@@ -899,13 +899,13 @@
       <c r="B7" s="10" t="n"/>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>маржа 23.0%</t>
+          <t>маржа 22.5%</t>
         </is>
       </c>
       <c r="D7" s="10" t="n"/>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>рентабельность 14.5%</t>
+          <t>рентабельность 14.0%</t>
         </is>
       </c>
       <c r="F7" s="10" t="n"/>
@@ -932,12 +932,12 @@
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="6">
-        <f>'ОДДС'!C12</f>
+        <f>'ОДДС'!C13</f>
         <v/>
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="8">
-        <f>'ОПиУ'!C33</f>
+        <f>'ОПиУ'!C32</f>
         <v/>
       </c>
       <c r="D10" s="7" t="n"/>
@@ -1004,18 +1004,18 @@
       </c>
       <c r="B16" s="15" t="n"/>
       <c r="C16" s="16">
-        <f>'ОПиУ'!C13</f>
+        <f>'ОПиУ'!C14</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>(−) Операционные расходы (ФОТ, админ, налоги)</t>
+          <t>(−) Операционные расходы (ФОТ, команд., админ, налоги)</t>
         </is>
       </c>
       <c r="C17" s="13">
-        <f>'ОПиУ'!C15+'ОПиУ'!C18+'ОПиУ'!C25</f>
+        <f>'ОПиУ'!C16+'ОПиУ'!C17+'ОПиУ'!C18+'ОПиУ'!C24</f>
         <v/>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B18" s="15" t="n"/>
       <c r="C18" s="16">
-        <f>'ОПиУ'!C26</f>
+        <f>'ОПиУ'!C25</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="C19" s="13">
-        <f>'ОПиУ'!C33-'ОПиУ'!C26</f>
+        <f>'ОПиУ'!C32-'ОПиУ'!C25</f>
         <v/>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B20" s="15" t="n"/>
       <c r="C20" s="16">
-        <f>'ОПиУ'!C33</f>
+        <f>'ОПиУ'!C32</f>
         <v/>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1245,11 +1245,11 @@
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Операторы вагонов (КТТ и др.)</t>
+          <t xml:space="preserve">    Прочие ж/д и ТЭУ услуги</t>
         </is>
       </c>
       <c r="C10" s="13">
-        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Операторы вагонов (КТТ и др.)")</f>
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Прочие ж/д и ТЭУ услуги")</f>
         <v/>
       </c>
       <c r="D10" s="22">
@@ -1260,11 +1260,11 @@
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Прочие ж/д и ТЭУ услуги</t>
+          <t xml:space="preserve">    Операторы вагонов (КТТ и др.)</t>
         </is>
       </c>
       <c r="C11" s="13">
-        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Прочие ж/д и ТЭУ услуги")</f>
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Операторы вагонов (КТТ и др.)")</f>
         <v/>
       </c>
       <c r="D11" s="22">
@@ -1288,51 +1288,51 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Страхование вагонов</t>
+        </is>
+      </c>
+      <c r="C13" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Страхование вагонов")</f>
+        <v/>
+      </c>
+      <c r="D13" s="22">
+        <f>IF($C$5=0,0,C13/$C$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>ВАЛОВАЯ ПРИБЫЛЬ</t>
         </is>
       </c>
-      <c r="B13" s="25" t="n"/>
-      <c r="C13" s="26">
+      <c r="B14" s="25" t="n"/>
+      <c r="C14" s="26">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D13" s="27">
-        <f>IF($C$5=0,0,C13/$C$5)</f>
+      <c r="D14" s="27">
+        <f>IF($C$5=0,0,C14/$C$5)</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>ОПЕРАЦИОННЫЕ РАСХОДЫ</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Фонд оплаты труда</t>
-        </is>
-      </c>
-      <c r="C15" s="13">
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Фонд оплаты труда (зарплата, премии)</t>
+        </is>
+      </c>
+      <c r="C16" s="13">
         <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"ФОТ")</f>
-        <v/>
-      </c>
-      <c r="D15" s="22">
-        <f>IF($C$5=0,0,C15/$C$5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Зарплата</t>
-        </is>
-      </c>
-      <c r="C16" s="13">
-        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Зарплата")</f>
         <v/>
       </c>
       <c r="D16" s="22">
@@ -1341,13 +1341,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Командировки и подотчёт</t>
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Командировки и подотчёт</t>
         </is>
       </c>
       <c r="C17" s="13">
-        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Командировки и подотчёт")</f>
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Командировки")</f>
         <v/>
       </c>
       <c r="D17" s="22">
@@ -1358,11 +1358,11 @@
     <row r="18">
       <c r="A18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Административные и офисные</t>
+          <t xml:space="preserve">    Административные и хозяйственные</t>
         </is>
       </c>
       <c r="C18" s="13">
-        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Админ/офис")</f>
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Админ/хоз")</f>
         <v/>
       </c>
       <c r="D18" s="22">
@@ -1373,11 +1373,11 @@
     <row r="19">
       <c r="A19" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Офис, аренда помещений, хоз.</t>
+          <t xml:space="preserve">        Офис, аренда, содержание</t>
         </is>
       </c>
       <c r="C19" s="13">
-        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Офис, аренда помещений, хоз.")</f>
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Офис, аренда, содержание")</f>
         <v/>
       </c>
       <c r="D19" s="22">
@@ -1403,11 +1403,11 @@
     <row r="21">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Связь и ИТ</t>
+          <t xml:space="preserve">        Связь, ИТ, ПО</t>
         </is>
       </c>
       <c r="C21" s="13">
-        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Связь и ИТ")</f>
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Связь, ИТ, ПО")</f>
         <v/>
       </c>
       <c r="D21" s="22">
@@ -1418,11 +1418,11 @@
     <row r="22">
       <c r="A22" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Маркетинг и представит.</t>
+          <t xml:space="preserve">        Маркетинг и реклама</t>
         </is>
       </c>
       <c r="C22" s="13">
-        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Маркетинг и представит.")</f>
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Маркетинг и реклама")</f>
         <v/>
       </c>
       <c r="D22" s="22">
@@ -1446,13 +1446,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Страхование</t>
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Налоги и отчисления</t>
         </is>
       </c>
       <c r="C24" s="13">
-        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Страхование")</f>
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Налоги")</f>
         <v/>
       </c>
       <c r="D24" s="22">
@@ -1461,51 +1461,51 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Налоги и отчисления</t>
-        </is>
-      </c>
-      <c r="C25" s="13">
-        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Налоги")</f>
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>ОПЕРАЦИОННАЯ ПРИБЫЛЬ (EBITDA-прокси)</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="n"/>
+      <c r="C25" s="26">
+        <f>C14+C16+C17+C18+C24</f>
         <v/>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="27">
         <f>IF($C$5=0,0,C25/$C$5)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>ОПЕРАЦИОННАЯ ПРИБЫЛЬ (EBITDA-прокси)</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="n"/>
-      <c r="C26" s="26">
-        <f>C13+C15+C18+C25</f>
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>ФИНАНСОВЫЕ РАСХОДЫ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Проценты по кредиту</t>
+        </is>
+      </c>
+      <c r="C27" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Проценты по кредиту")</f>
         <v/>
       </c>
-      <c r="D26" s="27">
-        <f>IF($C$5=0,0,C26/$C$5)</f>
+      <c r="D27" s="22">
+        <f>IF($C$5=0,0,C27/$C$5)</f>
         <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>ФИНАНСОВЫЕ РАСХОДЫ</t>
-        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Проценты по кредиту</t>
+          <t xml:space="preserve">    Финансовый лизинг</t>
         </is>
       </c>
       <c r="C28" s="13">
-        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Проценты по кредиту")</f>
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Финансовый лизинг")</f>
         <v/>
       </c>
       <c r="D28" s="22">
@@ -1516,11 +1516,11 @@
     <row r="29">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Финансовый лизинг</t>
+          <t xml:space="preserve">    Банковские комиссии</t>
         </is>
       </c>
       <c r="C29" s="13">
-        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Финансовый лизинг")</f>
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Банковские комиссии")</f>
         <v/>
       </c>
       <c r="D29" s="22">
@@ -1531,11 +1531,11 @@
     <row r="30">
       <c r="A30" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Банковские комиссии</t>
+          <t xml:space="preserve">    Проценты по депозиту (доход)</t>
         </is>
       </c>
       <c r="C30" s="13">
-        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Банковские комиссии")</f>
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$P$5:$P$442,"Проценты по депозиту")</f>
         <v/>
       </c>
       <c r="D30" s="22">
@@ -1544,13 +1544,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Проценты по депозиту (доход)</t>
-        </is>
-      </c>
-      <c r="C31" s="13">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$P$5:$P$442,"Проценты по депозиту")</f>
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>ПРОЧИЕ / РАЗОВЫЕ (возвраты авансов, спонсорство)</t>
+        </is>
+      </c>
+      <c r="C31" s="21">
+        <f>-(SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Прочее")-SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Прочее"))</f>
         <v/>
       </c>
       <c r="D31" s="22">
@@ -1559,49 +1559,34 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>ПРОЧИЕ / РАЗОВЫЕ (возвраты авансов, спонсорство)</t>
-        </is>
-      </c>
-      <c r="C32" s="21">
-        <f>-(SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Прочее")-SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Прочее"))</f>
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>ЧИСТЫЙ РЕЗУЛЬТАТ ПЕРИОДА (кассовый)</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="n"/>
+      <c r="C32" s="26">
+        <f>C25+C27+C28+C29+C30+C31</f>
         <v/>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="27">
         <f>IF($C$5=0,0,C32/$C$5)</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="24" t="inlineStr">
-        <is>
-          <t>ЧИСТЫЙ РЕЗУЛЬТАТ ПЕРИОДА (кассовый)</t>
-        </is>
-      </c>
-      <c r="B33" s="25" t="n"/>
-      <c r="C33" s="26">
-        <f>C26+C28+C29+C30+C31+C32</f>
-        <v/>
-      </c>
-      <c r="D33" s="27">
-        <f>IF($C$5=0,0,C33/$C$5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="44" customHeight="1">
-      <c r="A35" s="29" t="inlineStr">
+    <row r="34" ht="44" customHeight="1">
+      <c r="A34" s="29" t="inlineStr">
         <is>
           <t>Кассовый метод по банковским выпискам. Тело кредита (66,7 млн ₸) и выданные займы (48,1 млн ₸) — движение денег, отражены в ОДДС, а не в ОПиУ; в прибыли учтены только проценты по кредиту. Не учитывает амортизацию, начисления и незакрытые взаиморасчёты. Все суммы — формулы SUMIFS по листу «Реестр операций».</t>
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36"/>
-    <row r="37"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A35:D37"/>
+    <mergeCell ref="A34:D36"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1614,7 +1599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -1693,7 +1678,7 @@
     <row r="9">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>Оплата труда и командировки</t>
+          <t>Оплата труда (зарплата, премии)</t>
         </is>
       </c>
       <c r="C9" s="13">
@@ -1704,270 +1689,281 @@
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>Административные и офисные расходы</t>
+          <t>Командировки и подотчёт</t>
         </is>
       </c>
       <c r="C10" s="13">
-        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Админ/офис")</f>
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Командировки")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
         <is>
+          <t>Административные и хозяйственные расходы</t>
+        </is>
+      </c>
+      <c r="C11" s="13">
+        <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Админ/хоз")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
           <t>Налоги и отчисления</t>
         </is>
       </c>
-      <c r="C11" s="13">
+      <c r="C12" s="13">
         <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Налоги")</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>Чистый поток от операционной деятельности</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="26">
-        <f>SUM(C7:C11)</f>
+      <c r="B13" s="25" t="n"/>
+      <c r="C13" s="26">
+        <f>SUM(C7:C12)</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>ИНВЕСТИЦИОННАЯ ДЕЯТЕЛЬНОСТЬ</t>
         </is>
       </c>
-      <c r="B13" s="32" t="n"/>
-      <c r="C13" s="32" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="B14" s="32" t="n"/>
+      <c r="C14" s="32" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>Выдача займов (связанным лицам)</t>
         </is>
       </c>
-      <c r="C14" s="13">
+      <c r="C15" s="13">
         <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Выданные займы (связ. лица)")</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>Возврат ранее выданных займов</t>
         </is>
       </c>
-      <c r="C15" s="13">
+      <c r="C16" s="13">
         <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$P$5:$P$442,"Возврат выданных займов")</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>Чистый поток от инвестиционной деятельности</t>
         </is>
       </c>
-      <c r="B16" s="25" t="n"/>
-      <c r="C16" s="26">
-        <f>C14+C15</f>
+      <c r="B17" s="25" t="n"/>
+      <c r="C17" s="26">
+        <f>C15+C16</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="31" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>ФИНАНСОВАЯ ДЕЯТЕЛЬНОСТЬ</t>
         </is>
       </c>
-      <c r="B17" s="32" t="n"/>
-      <c r="C17" s="32" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="B18" s="32" t="n"/>
+      <c r="C18" s="32" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>Погашение тела кредита</t>
         </is>
       </c>
-      <c r="C18" s="13">
+      <c r="C19" s="13">
         <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Погашение кредита — тело")</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>Проценты по кредиту</t>
         </is>
       </c>
-      <c r="C19" s="13">
+      <c r="C20" s="13">
         <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Проценты по кредиту")</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>Финансовый лизинг</t>
         </is>
       </c>
-      <c r="C20" s="13">
+      <c r="C21" s="13">
         <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Финансовый лизинг")</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>Банковские комиссии</t>
         </is>
       </c>
-      <c r="C21" s="13">
+      <c r="C22" s="13">
         <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Банковские комиссии")</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="23" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>Проценты по депозиту (доход)</t>
         </is>
       </c>
-      <c r="C22" s="13">
+      <c r="C23" s="13">
         <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$P$5:$P$442,"Проценты по депозиту")</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="33" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="33" t="inlineStr">
         <is>
           <t>Чистый поток от финансовой деятельности</t>
         </is>
       </c>
-      <c r="B23" s="25" t="n"/>
-      <c r="C23" s="26">
-        <f>SUM(C18:C22)</f>
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="26">
+        <f>SUM(C19:C23)</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="31" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>ПРОЧИЕ / РАЗОВЫЕ ОПЕРАЦИИ</t>
         </is>
       </c>
-      <c r="B24" s="32" t="n"/>
-      <c r="C24" s="32" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="23" t="inlineStr">
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="32" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>Возврат средств контрагентам (авансы)</t>
         </is>
       </c>
-      <c r="C25" s="13">
+      <c r="C26" s="13">
         <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Возврат средств контрагенту")</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="23" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>Спонсорство / благотворительность</t>
         </is>
       </c>
-      <c r="C26" s="13">
+      <c r="C27" s="13">
         <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Спонсорство / благотвор.")</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="23" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>Прочие расходы</t>
         </is>
       </c>
-      <c r="C27" s="13">
+      <c r="C28" s="13">
         <f>-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Прочие расходы")</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="23" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>Прочие поступления</t>
         </is>
       </c>
-      <c r="C28" s="13">
+      <c r="C29" s="13">
         <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$P$5:$P$442,"Возврат средств")</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="33" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="33" t="inlineStr">
         <is>
           <t>Чистый поток от прочих операций</t>
         </is>
       </c>
-      <c r="B29" s="25" t="n"/>
-      <c r="C29" s="26">
-        <f>SUM(C25:C28)</f>
+      <c r="B30" s="25" t="n"/>
+      <c r="C30" s="26">
+        <f>SUM(C26:C29)</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="30" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="30" t="inlineStr">
         <is>
           <t>Перемещения на прочие счета Группы + конвертация валют (нетто)</t>
         </is>
       </c>
-      <c r="C30" s="21">
+      <c r="C31" s="21">
         <f>(SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$N$5:$N$442,"Внутренний перевод")-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внутренний перевод"))+(SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$N$5:$N$442,"Конвертация валют")-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Конвертация валют"))</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="33" t="inlineStr">
-        <is>
-          <t>ЧИСТОЕ ИЗМЕНЕНИЕ ДЕНЕЖНЫХ СРЕДСТВ</t>
-        </is>
-      </c>
-      <c r="B31" s="25" t="n"/>
-      <c r="C31" s="26">
-        <f>C12+C16+C23+C29+C30</f>
-        <v/>
-      </c>
-    </row>
     <row r="32">
       <c r="A32" s="33" t="inlineStr">
         <is>
-          <t>Остаток денежных средств на конец периода</t>
+          <t>ЧИСТОЕ ИЗМЕНЕНИЕ ДЕНЕЖНЫХ СРЕДСТВ</t>
         </is>
       </c>
       <c r="B32" s="25" t="n"/>
       <c r="C32" s="26">
-        <f>C5+C31</f>
+        <f>C13+C17+C24+C30+C31</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="44" customHeight="1">
-      <c r="A34" s="29" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="33" t="inlineStr">
+        <is>
+          <t>Остаток денежных средств на конец периода</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="n"/>
+      <c r="C33" s="26">
+        <f>C5+C32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="44" customHeight="1">
+      <c r="A35" s="29" t="inlineStr">
         <is>
           <t>Сверка сходится: остаток на начало 73 256 ₸ + чистое изменение = остаток на конец ≈ 0 (см. лист «Денежные средства»). Строка «Перемещения на прочие счета Группы + конвертация» балансирует переводы на счета вне этих выписок и курсовые разницы. Все суммы — формулы по реестру.</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36"/>
+    <row r="37"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A34:C36"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A35:C37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1979,7 +1975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2109,12 +2105,12 @@
     <row r="9">
       <c r="A9" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Операторы вагонов (КТТ и др.)</t>
+          <t xml:space="preserve">    Прочие ж/д и ТЭУ услуги</t>
         </is>
       </c>
       <c r="B9" s="38" t="n"/>
       <c r="C9" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Операторы вагонов (КТТ и др.)")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Прочие ж/д и ТЭУ услуги")</f>
         <v/>
       </c>
       <c r="D9" s="40">
@@ -2129,12 +2125,12 @@
     <row r="10">
       <c r="A10" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Прочие ж/д и ТЭУ услуги</t>
+          <t xml:space="preserve">    Операторы вагонов (КТТ и др.)</t>
         </is>
       </c>
       <c r="B10" s="38" t="n"/>
       <c r="C10" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Прочие ж/д и ТЭУ услуги")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Операторы вагонов (КТТ и др.)")</f>
         <v/>
       </c>
       <c r="D10" s="40">
@@ -2167,41 +2163,41 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Страхование вагонов</t>
+        </is>
+      </c>
+      <c r="B12" s="38" t="n"/>
+      <c r="C12" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Страхование вагонов")</f>
+        <v/>
+      </c>
+      <c r="D12" s="40">
+        <f>C12/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E12" s="40">
+        <f>C12/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>ФОТ</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="16">
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="16">
         <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"ФОТ")</f>
         <v/>
       </c>
-      <c r="D12" s="35">
-        <f>C12/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
-        <v/>
-      </c>
-      <c r="E12" s="36">
-        <f>C12/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Зарплата</t>
-        </is>
-      </c>
-      <c r="B13" s="38" t="n"/>
-      <c r="C13" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Зарплата")</f>
-        <v/>
-      </c>
-      <c r="D13" s="40">
+      <c r="D13" s="35">
         <f>C13/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
         <v/>
       </c>
-      <c r="E13" s="40">
+      <c r="E13" s="36">
         <f>C13/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
         <v/>
       </c>
@@ -2209,12 +2205,12 @@
     <row r="14">
       <c r="A14" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Командировки и подотчёт</t>
+          <t xml:space="preserve">    Зарплата</t>
         </is>
       </c>
       <c r="B14" s="38" t="n"/>
       <c r="C14" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Командировки и подотчёт")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Зарплата")</f>
         <v/>
       </c>
       <c r="D14" s="40">
@@ -2229,12 +2225,12 @@
     <row r="15">
       <c r="A15" s="34" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="B15" s="15" t="n"/>
       <c r="C15" s="16">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Админ/офис")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Командировки")</f>
         <v/>
       </c>
       <c r="D15" s="35">
@@ -2249,12 +2245,12 @@
     <row r="16">
       <c r="A16" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Офис, аренда помещений, хоз.</t>
+          <t xml:space="preserve">    Командировки и подотчёт</t>
         </is>
       </c>
       <c r="B16" s="38" t="n"/>
       <c r="C16" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Офис, аренда помещений, хоз.")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Командировки и подотчёт")</f>
         <v/>
       </c>
       <c r="D16" s="40">
@@ -2267,21 +2263,21 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Проф. услуги (бухг./юр./конс.)</t>
-        </is>
-      </c>
-      <c r="B17" s="38" t="n"/>
-      <c r="C17" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Проф. услуги (бухг./юр./конс.)")</f>
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>Админ/хоз</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="16">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Админ/хоз")</f>
         <v/>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="35">
         <f>C17/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
         <v/>
       </c>
-      <c r="E17" s="40">
+      <c r="E17" s="36">
         <f>C17/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
         <v/>
       </c>
@@ -2289,12 +2285,12 @@
     <row r="18">
       <c r="A18" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Связь и ИТ</t>
+          <t xml:space="preserve">    Офис, аренда, содержание</t>
         </is>
       </c>
       <c r="B18" s="38" t="n"/>
       <c r="C18" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Связь и ИТ")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Офис, аренда, содержание")</f>
         <v/>
       </c>
       <c r="D18" s="40">
@@ -2309,12 +2305,12 @@
     <row r="19">
       <c r="A19" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Маркетинг и представит.</t>
+          <t xml:space="preserve">    Проф. услуги (бухг./юр./конс.)</t>
         </is>
       </c>
       <c r="B19" s="38" t="n"/>
       <c r="C19" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Маркетинг и представит.")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Проф. услуги (бухг./юр./конс.)")</f>
         <v/>
       </c>
       <c r="D19" s="40">
@@ -2329,12 +2325,12 @@
     <row r="20">
       <c r="A20" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Хоз. расходы и материалы</t>
+          <t xml:space="preserve">    Связь, ИТ, ПО</t>
         </is>
       </c>
       <c r="B20" s="38" t="n"/>
       <c r="C20" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Хоз. расходы и материалы")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Связь, ИТ, ПО")</f>
         <v/>
       </c>
       <c r="D20" s="40">
@@ -2349,12 +2345,12 @@
     <row r="21">
       <c r="A21" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Страхование</t>
+          <t xml:space="preserve">    Маркетинг и реклама</t>
         </is>
       </c>
       <c r="B21" s="38" t="n"/>
       <c r="C21" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Страхование")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Маркетинг и реклама")</f>
         <v/>
       </c>
       <c r="D21" s="40">
@@ -2367,81 +2363,81 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="34" t="inlineStr">
+      <c r="A22" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Хоз. расходы и материалы</t>
+        </is>
+      </c>
+      <c r="B22" s="38" t="n"/>
+      <c r="C22" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Хоз. расходы и материалы")</f>
+        <v/>
+      </c>
+      <c r="D22" s="40">
+        <f>C22/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E22" s="40">
+        <f>C22/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>Налоги</t>
         </is>
       </c>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="16">
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="16">
         <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Налоги")</f>
         <v/>
       </c>
-      <c r="D22" s="35">
-        <f>C22/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+      <c r="D23" s="35">
+        <f>C23/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
         <v/>
       </c>
-      <c r="E22" s="36">
-        <f>C22/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+      <c r="E23" s="36">
+        <f>C23/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="37" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">    Налоги и отчисления</t>
         </is>
       </c>
-      <c r="B23" s="38" t="n"/>
-      <c r="C23" s="39">
+      <c r="B24" s="38" t="n"/>
+      <c r="C24" s="39">
         <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Налоги и отчисления")</f>
         <v/>
       </c>
-      <c r="D23" s="40">
-        <f>C23/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+      <c r="D24" s="40">
+        <f>C24/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
         <v/>
       </c>
-      <c r="E23" s="40">
-        <f>C23/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+      <c r="E24" s="40">
+        <f>C24/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="34" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>Финансовые</t>
         </is>
       </c>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="16">
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="16">
         <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Финансовые")</f>
         <v/>
       </c>
-      <c r="D24" s="35">
-        <f>C24/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
-        <v/>
-      </c>
-      <c r="E24" s="36">
-        <f>C24/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Погашение кредита — тело</t>
-        </is>
-      </c>
-      <c r="B25" s="38" t="n"/>
-      <c r="C25" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Погашение кредита — тело")</f>
-        <v/>
-      </c>
-      <c r="D25" s="40">
+      <c r="D25" s="35">
         <f>C25/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
         <v/>
       </c>
-      <c r="E25" s="40">
+      <c r="E25" s="36">
         <f>C25/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
         <v/>
       </c>
@@ -2449,12 +2445,12 @@
     <row r="26">
       <c r="A26" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Выданные займы (связ. лица)</t>
+          <t xml:space="preserve">    Погашение кредита — тело</t>
         </is>
       </c>
       <c r="B26" s="38" t="n"/>
       <c r="C26" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Выданные займы (связ. лица)")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Погашение кредита — тело")</f>
         <v/>
       </c>
       <c r="D26" s="40">
@@ -2469,12 +2465,12 @@
     <row r="27">
       <c r="A27" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Финансовый лизинг</t>
+          <t xml:space="preserve">    Выданные займы (связ. лица)</t>
         </is>
       </c>
       <c r="B27" s="38" t="n"/>
       <c r="C27" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Финансовый лизинг")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Выданные займы (связ. лица)")</f>
         <v/>
       </c>
       <c r="D27" s="40">
@@ -2489,12 +2485,12 @@
     <row r="28">
       <c r="A28" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Проценты по кредиту</t>
+          <t xml:space="preserve">    Финансовый лизинг</t>
         </is>
       </c>
       <c r="B28" s="38" t="n"/>
       <c r="C28" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Проценты по кредиту")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Финансовый лизинг")</f>
         <v/>
       </c>
       <c r="D28" s="40">
@@ -2509,12 +2505,12 @@
     <row r="29">
       <c r="A29" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Банковские комиссии</t>
+          <t xml:space="preserve">    Проценты по кредиту</t>
         </is>
       </c>
       <c r="B29" s="38" t="n"/>
       <c r="C29" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Банковские комиссии")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Проценты по кредиту")</f>
         <v/>
       </c>
       <c r="D29" s="40">
@@ -2527,41 +2523,41 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="34" t="inlineStr">
+      <c r="A30" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Банковские комиссии</t>
+        </is>
+      </c>
+      <c r="B30" s="38" t="n"/>
+      <c r="C30" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Банковские комиссии")</f>
+        <v/>
+      </c>
+      <c r="D30" s="40">
+        <f>C30/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E30" s="40">
+        <f>C30/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="inlineStr">
         <is>
           <t>Прочее</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n"/>
-      <c r="C30" s="16">
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="16">
         <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Прочее")</f>
         <v/>
       </c>
-      <c r="D30" s="35">
-        <f>C30/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
-        <v/>
-      </c>
-      <c r="E30" s="36">
-        <f>C30/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Возврат средств контрагенту</t>
-        </is>
-      </c>
-      <c r="B31" s="38" t="n"/>
-      <c r="C31" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Возврат средств контрагенту")</f>
-        <v/>
-      </c>
-      <c r="D31" s="40">
+      <c r="D31" s="35">
         <f>C31/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
         <v/>
       </c>
-      <c r="E31" s="40">
+      <c r="E31" s="36">
         <f>C31/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
         <v/>
       </c>
@@ -2569,12 +2565,12 @@
     <row r="32">
       <c r="A32" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Прочие расходы</t>
+          <t xml:space="preserve">    Возврат средств контрагенту</t>
         </is>
       </c>
       <c r="B32" s="38" t="n"/>
       <c r="C32" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Прочие расходы")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Возврат средств контрагенту")</f>
         <v/>
       </c>
       <c r="D32" s="40">
@@ -2589,12 +2585,12 @@
     <row r="33">
       <c r="A33" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Спонсорство / благотвор.</t>
+          <t xml:space="preserve">    Прочие расходы</t>
         </is>
       </c>
       <c r="B33" s="38" t="n"/>
       <c r="C33" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Спонсорство / благотвор.")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Прочие расходы")</f>
         <v/>
       </c>
       <c r="D33" s="40">
@@ -2607,21 +2603,41 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="41" t="inlineStr">
+      <c r="A34" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Спонсорство / благотвор.</t>
+        </is>
+      </c>
+      <c r="B34" s="38" t="n"/>
+      <c r="C34" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$P$5:$P$442,"Спонсорство / благотвор.")</f>
+        <v/>
+      </c>
+      <c r="D34" s="40">
+        <f>C34/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
+        <v/>
+      </c>
+      <c r="E34" s="40">
+        <f>C34/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="41" t="inlineStr">
         <is>
           <t>ИТОГО расход (внешний)</t>
         </is>
       </c>
-      <c r="B34" s="42" t="n"/>
-      <c r="C34" s="43">
+      <c r="B35" s="42" t="n"/>
+      <c r="C35" s="43">
         <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внешняя операция")</f>
         <v/>
       </c>
-      <c r="D34" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="44">
-        <f>C34/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+      <c r="D35" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="44">
+        <f>C35/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
         <v/>
       </c>
     </row>
@@ -2635,532 +2651,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Выручка по клиентам (все 25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Все контрагенты-плательщики за услуги · формулы SUMIFS по реестру</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>Контрагент</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>Сумма, ₸</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>% выручки</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="46" t="inlineStr">
-        <is>
-          <t>ТОО «QAZAQ-ASTYQ GROUP»</t>
-        </is>
-      </c>
-      <c r="C5" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО «QAZAQ-ASTYQ GROUP»",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D5" s="40">
-        <f>C5/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="46" t="inlineStr">
-        <is>
-          <t>ALBATAREEQ TRADING LLC (ОАЭ)</t>
-        </is>
-      </c>
-      <c r="C6" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ALBATAREEQ TRADING LLC (ОАЭ)",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D6" s="40">
-        <f>C6/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="46" t="inlineStr">
-        <is>
-          <t>ТОО «Altyn Shyghys»</t>
-        </is>
-      </c>
-      <c r="C7" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО «Altyn Shyghys»",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D7" s="40">
-        <f>C7/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="45" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="46" t="inlineStr">
-        <is>
-          <t>ТОО ROYAL EXPORT</t>
-        </is>
-      </c>
-      <c r="C8" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ROYAL EXPORT",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D8" s="40">
-        <f>C8/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="46" t="inlineStr">
-        <is>
-          <t>ТОО "ШыгысАгроТорг"</t>
-        </is>
-      </c>
-      <c r="C9" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""ШыгысАгроТорг""",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D9" s="40">
-        <f>C9/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="45" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="46" t="inlineStr">
-        <is>
-          <t>ТОО "Экспорт-М"</t>
-        </is>
-      </c>
-      <c r="C10" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Экспорт-М""",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D10" s="40">
-        <f>C10/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="45" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="46" t="inlineStr">
-        <is>
-          <t>ТОО REGAL EXPORT</t>
-        </is>
-      </c>
-      <c r="C11" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО REGAL EXPORT",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D11" s="40">
-        <f>C11/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="45" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="46" t="inlineStr">
-        <is>
-          <t>ТОО East Agro Company</t>
-        </is>
-      </c>
-      <c r="C12" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО East Agro Company",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D12" s="40">
-        <f>C12/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="45" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="46" t="inlineStr">
-        <is>
-          <t>ТОО "УСТЬ-КАМЕНОГОРСКИЙ МАСЛО-ЭКСТРАКЦИОННЫЙ</t>
-        </is>
-      </c>
-      <c r="C13" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""УСТЬ-КАМЕНОГОРСКИЙ МАСЛО-ЭКСТРАКЦИОННЫЙ",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D13" s="40">
-        <f>C13/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="45" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="46" t="inlineStr">
-        <is>
-          <t>ТОО Агро-Трейд-2030</t>
-        </is>
-      </c>
-      <c r="C14" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО Агро-Трейд-2030",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D14" s="40">
-        <f>C14/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="45" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="46" t="inlineStr">
-        <is>
-          <t>ТОО Евразиан Каспиан Транс</t>
-        </is>
-      </c>
-      <c r="C15" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО Евразиан Каспиан Транс",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D15" s="40">
-        <f>C15/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="45" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="46" t="inlineStr">
-        <is>
-          <t>ТОО "GREENLIGHTS (ГРИНЛАЙТС)"</t>
-        </is>
-      </c>
-      <c r="C16" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""GREENLIGHTS (ГРИНЛАЙТС)""",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D16" s="40">
-        <f>C16/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="45" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="46" t="inlineStr">
-        <is>
-          <t>ТОО Темир Экспресс Логистик</t>
-        </is>
-      </c>
-      <c r="C17" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО Темир Экспресс Логистик",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D17" s="40">
-        <f>C17/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="45" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="46" t="inlineStr">
-        <is>
-          <t>ТОО "TimeAgro"</t>
-        </is>
-      </c>
-      <c r="C18" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""TimeAgro""",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D18" s="40">
-        <f>C18/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="45" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="46" t="inlineStr">
-        <is>
-          <t>ТОВАРИЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ</t>
-        </is>
-      </c>
-      <c r="C19" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОВАРИЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D19" s="40">
-        <f>C19/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="45" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="46" t="inlineStr">
-        <is>
-          <t>ТОО ALTAI MAI</t>
-        </is>
-      </c>
-      <c r="C20" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ALTAI MAI",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D20" s="40">
-        <f>C20/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="45" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="46" t="inlineStr">
-        <is>
-          <t>ТОО «Atasu Global Trans»</t>
-        </is>
-      </c>
-      <c r="C21" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО «Atasu Global Trans»",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D21" s="40">
-        <f>C21/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="45" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="46" t="inlineStr">
-        <is>
-          <t>ТОО Kaz-Smart Logistics</t>
-        </is>
-      </c>
-      <c r="C22" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО Kaz-Smart Logistics",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D22" s="40">
-        <f>C22/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="45" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="46" t="inlineStr">
-        <is>
-          <t>ТОО EASY BOX</t>
-        </is>
-      </c>
-      <c r="C23" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО EASY BOX",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D23" s="40">
-        <f>C23/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="45" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="46" t="inlineStr">
-        <is>
-          <t>ТОО "AsstrА Almaty" (АсстрА Алматы)</t>
-        </is>
-      </c>
-      <c r="C24" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""AsstrА Almaty"" (АсстрА Алматы)",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D24" s="40">
-        <f>C24/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="45" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="46" t="inlineStr">
-        <is>
-          <t>ТОО Rhenus Intermodal Systems</t>
-        </is>
-      </c>
-      <c r="C25" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО Rhenus Intermodal Systems",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D25" s="40">
-        <f>C25/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="45" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="46" t="inlineStr">
-        <is>
-          <t>ТОО Каз Алтын Групп</t>
-        </is>
-      </c>
-      <c r="C26" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО Каз Алтын Групп",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D26" s="40">
-        <f>C26/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="45" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="46" t="inlineStr">
-        <is>
-          <t>ТОО "Максат-2030"</t>
-        </is>
-      </c>
-      <c r="C27" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Максат-2030""",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D27" s="40">
-        <f>C27/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="45" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="46" t="inlineStr">
-        <is>
-          <t>ТОО "FRS logistics"</t>
-        </is>
-      </c>
-      <c r="C28" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""FRS logistics""",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D28" s="40">
-        <f>C28/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="45" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="46" t="inlineStr">
-        <is>
-          <t>Данияр Алим</t>
-        </is>
-      </c>
-      <c r="C29" s="39">
-        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"Данияр Алим",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-      <c r="D29" s="40">
-        <f>C29/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="25" t="n"/>
-      <c r="B30" s="47" t="inlineStr">
-        <is>
-          <t>ИТОГО (25 контрагентов)</t>
-        </is>
-      </c>
-      <c r="C30" s="26">
-        <f>SUM(C5:C29)</f>
-        <v/>
-      </c>
-      <c r="D30" s="48">
-        <f>C30/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3178,7 +2668,515 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Затраты по поставщикам (все 24)</t>
+          <t>Выручка по клиентам (все 24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Все контрагенты-плательщики за услуги · формулы SUMIFS по реестру</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>Контрагент</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>Сумма, ₸</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>% выручки</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="46" t="inlineStr">
+        <is>
+          <t>ТОО «QAZAQ-ASTYQ GROUP»</t>
+        </is>
+      </c>
+      <c r="C5" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО «QAZAQ-ASTYQ GROUP»",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D5" s="40">
+        <f>C5/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="46" t="inlineStr">
+        <is>
+          <t>ALBATAREEQ TRADING LLC (ОАЭ)</t>
+        </is>
+      </c>
+      <c r="C6" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ALBATAREEQ TRADING LLC (ОАЭ)",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D6" s="40">
+        <f>C6/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="46" t="inlineStr">
+        <is>
+          <t>ТОО «Altyn Shyghys»</t>
+        </is>
+      </c>
+      <c r="C7" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО «Altyn Shyghys»",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D7" s="40">
+        <f>C7/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="46" t="inlineStr">
+        <is>
+          <t>ТОО ROYAL EXPORT</t>
+        </is>
+      </c>
+      <c r="C8" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ROYAL EXPORT",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D8" s="40">
+        <f>C8/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "ШыгысАгроТорг"</t>
+        </is>
+      </c>
+      <c r="C9" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""ШыгысАгроТорг""",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D9" s="40">
+        <f>C9/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "Экспорт-М"</t>
+        </is>
+      </c>
+      <c r="C10" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Экспорт-М""",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D10" s="40">
+        <f>C10/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="46" t="inlineStr">
+        <is>
+          <t>ТОО REGAL EXPORT</t>
+        </is>
+      </c>
+      <c r="C11" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО REGAL EXPORT",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D11" s="40">
+        <f>C11/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="46" t="inlineStr">
+        <is>
+          <t>ТОО East Agro Company</t>
+        </is>
+      </c>
+      <c r="C12" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО East Agro Company",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D12" s="40">
+        <f>C12/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "УСТЬ-КАМЕНОГОРСКИЙ МАСЛО-ЭКСТРАКЦИОННЫЙ</t>
+        </is>
+      </c>
+      <c r="C13" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""УСТЬ-КАМЕНОГОРСКИЙ МАСЛО-ЭКСТРАКЦИОННЫЙ",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D13" s="40">
+        <f>C13/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="46" t="inlineStr">
+        <is>
+          <t>ТОО Агро-Трейд-2030</t>
+        </is>
+      </c>
+      <c r="C14" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО Агро-Трейд-2030",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D14" s="40">
+        <f>C14/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="46" t="inlineStr">
+        <is>
+          <t>ТОО Евразиан Каспиан Транс</t>
+        </is>
+      </c>
+      <c r="C15" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО Евразиан Каспиан Транс",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D15" s="40">
+        <f>C15/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "GREENLIGHTS (ГРИНЛАЙТС)"</t>
+        </is>
+      </c>
+      <c r="C16" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""GREENLIGHTS (ГРИНЛАЙТС)""",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D16" s="40">
+        <f>C16/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="45" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="46" t="inlineStr">
+        <is>
+          <t>ТОО Темир Экспресс Логистик</t>
+        </is>
+      </c>
+      <c r="C17" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО Темир Экспресс Логистик",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D17" s="40">
+        <f>C17/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="45" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "TimeAgro"</t>
+        </is>
+      </c>
+      <c r="C18" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""TimeAgro""",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D18" s="40">
+        <f>C18/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="46" t="inlineStr">
+        <is>
+          <t>ТОВАРИЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ</t>
+        </is>
+      </c>
+      <c r="C19" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОВАРИЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D19" s="40">
+        <f>C19/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="46" t="inlineStr">
+        <is>
+          <t>ТОО ALTAI MAI</t>
+        </is>
+      </c>
+      <c r="C20" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ALTAI MAI",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D20" s="40">
+        <f>C20/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="45" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="46" t="inlineStr">
+        <is>
+          <t>ТОО «Atasu Global Trans»</t>
+        </is>
+      </c>
+      <c r="C21" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО «Atasu Global Trans»",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D21" s="40">
+        <f>C21/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="45" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="46" t="inlineStr">
+        <is>
+          <t>ТОО Kaz-Smart Logistics</t>
+        </is>
+      </c>
+      <c r="C22" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО Kaz-Smart Logistics",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D22" s="40">
+        <f>C22/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="45" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="46" t="inlineStr">
+        <is>
+          <t>ТОО EASY BOX</t>
+        </is>
+      </c>
+      <c r="C23" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО EASY BOX",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D23" s="40">
+        <f>C23/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "AsstrА Almaty" (АсстрА Алматы)</t>
+        </is>
+      </c>
+      <c r="C24" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""AsstrА Almaty"" (АсстрА Алматы)",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D24" s="40">
+        <f>C24/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="45" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="46" t="inlineStr">
+        <is>
+          <t>ТОО Rhenus Intermodal Systems</t>
+        </is>
+      </c>
+      <c r="C25" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО Rhenus Intermodal Systems",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D25" s="40">
+        <f>C25/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="45" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="46" t="inlineStr">
+        <is>
+          <t>ТОО Каз Алтын Групп</t>
+        </is>
+      </c>
+      <c r="C26" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО Каз Алтын Групп",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D26" s="40">
+        <f>C26/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="45" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "Максат-2030"</t>
+        </is>
+      </c>
+      <c r="C27" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Максат-2030""",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D27" s="40">
+        <f>C27/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="45" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "FRS logistics"</t>
+        </is>
+      </c>
+      <c r="C28" s="39">
+        <f>SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""FRS logistics""",'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+      <c r="D28" s="40">
+        <f>C28/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="25" t="n"/>
+      <c r="B29" s="47" t="inlineStr">
+        <is>
+          <t>ИТОГО (24 контрагентов)</t>
+        </is>
+      </c>
+      <c r="C29" s="26">
+        <f>SUM(C5:C28)</f>
+        <v/>
+      </c>
+      <c r="D29" s="48">
+        <f>C29/SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$O$5:$O$442,"Выручка")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Затраты по поставщикам (все 26)</t>
         </is>
       </c>
     </row>
@@ -3451,11 +3449,11 @@
       </c>
       <c r="B18" s="46" t="inlineStr">
         <is>
-          <t>ТОО "Нұр-Альфинур"</t>
+          <t>ТОО "Рейл Транспортейшн"</t>
         </is>
       </c>
       <c r="C18" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Нұр-Альфинур""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Рейл Транспортейшн""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
         <v/>
       </c>
       <c r="D18" s="40">
@@ -3469,11 +3467,11 @@
       </c>
       <c r="B19" s="46" t="inlineStr">
         <is>
-          <t>ТОО "Asia Railways Tracking Service (Азия Рэ</t>
+          <t>ТОО "Нұр-Альфинур"</t>
         </is>
       </c>
       <c r="C19" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Asia Railways Tracking Service (Азия Рэ",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Нұр-Альфинур""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
         <v/>
       </c>
       <c r="D19" s="40">
@@ -3487,11 +3485,11 @@
       </c>
       <c r="B20" s="46" t="inlineStr">
         <is>
-          <t>Turkmen Demiryol Express (Туркм.)</t>
+          <t>ТОО "Asia Railways Tracking Service (Азия Рэ</t>
         </is>
       </c>
       <c r="C20" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"Turkmen Demiryol Express (Туркм.)",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Asia Railways Tracking Service (Азия Рэ",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
         <v/>
       </c>
       <c r="D20" s="40">
@@ -3505,11 +3503,11 @@
       </c>
       <c r="B21" s="46" t="inlineStr">
         <is>
-          <t>ТОО ""SK RAILWAY Service""</t>
+          <t>Turkmen Demiryol Express (Туркм.)</t>
         </is>
       </c>
       <c r="C21" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО """"SK RAILWAY Service""""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"Turkmen Demiryol Express (Туркм.)",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
         <v/>
       </c>
       <c r="D21" s="40">
@@ -3523,11 +3521,11 @@
       </c>
       <c r="B22" s="46" t="inlineStr">
         <is>
-          <t>филиал акционерного общества "Национальная к</t>
+          <t>ТОО "Kumo Trans"</t>
         </is>
       </c>
       <c r="C22" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"филиал акционерного общества ""Национальная к",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Kumo Trans""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
         <v/>
       </c>
       <c r="D22" s="40">
@@ -3541,11 +3539,11 @@
       </c>
       <c r="B23" s="46" t="inlineStr">
         <is>
-          <t>ТОО "ТОР Арыс"</t>
+          <t>ТОО ""SK RAILWAY Service""</t>
         </is>
       </c>
       <c r="C23" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""ТОР Арыс""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО """"SK RAILWAY Service""""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
         <v/>
       </c>
       <c r="D23" s="40">
@@ -3559,11 +3557,11 @@
       </c>
       <c r="B24" s="46" t="inlineStr">
         <is>
-          <t>ТОО "Olivin.kz (Оливин.кз)"</t>
+          <t>Акционерное общество "Страховая компания "Ев</t>
         </is>
       </c>
       <c r="C24" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Olivin.kz (Оливин.кз)""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"Акционерное общество ""Страховая компания ""Ев",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
         <v/>
       </c>
       <c r="D24" s="40">
@@ -3577,11 +3575,11 @@
       </c>
       <c r="B25" s="46" t="inlineStr">
         <is>
-          <t>Производственный кооператив "ИБРАЕВ+К"</t>
+          <t>филиал акционерного общества "Национальная к</t>
         </is>
       </c>
       <c r="C25" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"Производственный кооператив ""ИБРАЕВ+К""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"филиал акционерного общества ""Национальная к",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
         <v/>
       </c>
       <c r="D25" s="40">
@@ -3595,11 +3593,11 @@
       </c>
       <c r="B26" s="46" t="inlineStr">
         <is>
-          <t>ТОО "Объединенное железнодорожное хозяйство"</t>
+          <t>ТОО "ТОР Арыс"</t>
         </is>
       </c>
       <c r="C26" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Объединенное железнодорожное хозяйство""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""ТОР Арыс""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
         <v/>
       </c>
       <c r="D26" s="40">
@@ -3613,11 +3611,11 @@
       </c>
       <c r="B27" s="46" t="inlineStr">
         <is>
-          <t>ТОО "АФ АГМ-Табыс"</t>
+          <t>Производственный кооператив "ИБРАЕВ+К"</t>
         </is>
       </c>
       <c r="C27" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""АФ АГМ-Табыс""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"Производственный кооператив ""ИБРАЕВ+К""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
         <v/>
       </c>
       <c r="D27" s="40">
@@ -3631,11 +3629,11 @@
       </c>
       <c r="B28" s="46" t="inlineStr">
         <is>
-          <t>Филиал акционерного общества «Национальная к</t>
+          <t>ТОО "Объединенное железнодорожное хозяйство"</t>
         </is>
       </c>
       <c r="C28" s="39">
-        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"Филиал акционерного общества «Национальная к",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""Объединенное железнодорожное хозяйство""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
         <v/>
       </c>
       <c r="D28" s="40">
@@ -3644,18 +3642,54 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25" t="n"/>
-      <c r="B29" s="47" t="inlineStr">
-        <is>
-          <t>ИТОГО (24 контрагентов)</t>
-        </is>
-      </c>
-      <c r="C29" s="26">
-        <f>SUM(C5:C28)</f>
+      <c r="A29" s="45" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="46" t="inlineStr">
+        <is>
+          <t>ТОО "АФ АГМ-Табыс"</t>
+        </is>
+      </c>
+      <c r="C29" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"ТОО ""АФ АГМ-Табыс""",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
         <v/>
       </c>
-      <c r="D29" s="48">
+      <c r="D29" s="40">
         <f>C29/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="45" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="46" t="inlineStr">
+        <is>
+          <t>Филиал акционерного общества «Национальная к</t>
+        </is>
+      </c>
+      <c r="C30" s="39">
+        <f>SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$Q$5:$Q$442,"Филиал акционерного общества «Национальная к",'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+      <c r="D30" s="40">
+        <f>C30/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="n"/>
+      <c r="B31" s="47" t="inlineStr">
+        <is>
+          <t>ИТОГО (26 контрагентов)</t>
+        </is>
+      </c>
+      <c r="C31" s="26">
+        <f>SUM(C5:C30)</f>
+        <v/>
+      </c>
+      <c r="D31" s="48">
+        <f>C31/SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$O$5:$O$442,"Себестоимость")</f>
         <v/>
       </c>
     </row>
@@ -4168,7 +4202,7 @@
       </c>
       <c r="O5" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P5" s="55" t="inlineStr">
@@ -4241,7 +4275,7 @@
       </c>
       <c r="O6" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P6" s="55" t="inlineStr">
@@ -4314,7 +4348,7 @@
       </c>
       <c r="O7" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P7" s="55" t="inlineStr">
@@ -4387,12 +4421,12 @@
       </c>
       <c r="O8" s="55" t="inlineStr">
         <is>
-          <t>Себестоимость</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P8" s="55" t="inlineStr">
         <is>
-          <t>Ремонт вагонов и узлов</t>
+          <t>Хоз. расходы и материалы</t>
         </is>
       </c>
       <c r="Q8" s="55" t="inlineStr">
@@ -5588,7 +5622,7 @@
       </c>
       <c r="O25" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P25" s="55" t="inlineStr">
@@ -5661,7 +5695,7 @@
       </c>
       <c r="O26" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P26" s="55" t="inlineStr">
@@ -5807,7 +5841,7 @@
       </c>
       <c r="O28" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P28" s="55" t="inlineStr">
@@ -7556,12 +7590,12 @@
       </c>
       <c r="O53" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P53" s="55" t="inlineStr">
         <is>
-          <t>Связь и ИТ</t>
+          <t>Связь, ИТ, ПО</t>
         </is>
       </c>
       <c r="Q53" s="55" t="inlineStr">
@@ -7629,12 +7663,12 @@
       </c>
       <c r="O54" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P54" s="55" t="inlineStr">
         <is>
-          <t>Маркетинг и представит.</t>
+          <t>Маркетинг и реклама</t>
         </is>
       </c>
       <c r="Q54" s="55" t="inlineStr">
@@ -7775,12 +7809,12 @@
       </c>
       <c r="O56" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P56" s="55" t="inlineStr">
         <is>
-          <t>Проф. услуги (бухг./юр./конс.)</t>
+          <t>Маркетинг и реклама</t>
         </is>
       </c>
       <c r="Q56" s="55" t="inlineStr">
@@ -7848,12 +7882,12 @@
       </c>
       <c r="O57" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P57" s="55" t="inlineStr">
         <is>
-          <t>Офис, аренда помещений, хоз.</t>
+          <t>Офис, аренда, содержание</t>
         </is>
       </c>
       <c r="Q57" s="55" t="inlineStr">
@@ -7994,12 +8028,12 @@
       </c>
       <c r="O59" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P59" s="55" t="inlineStr">
         <is>
-          <t>Проф. услуги (бухг./юр./конс.)</t>
+          <t>Связь, ИТ, ПО</t>
         </is>
       </c>
       <c r="Q59" s="55" t="inlineStr">
@@ -8067,7 +8101,7 @@
       </c>
       <c r="O60" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P60" s="55" t="inlineStr">
@@ -8140,12 +8174,12 @@
       </c>
       <c r="O61" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P61" s="55" t="inlineStr">
         <is>
-          <t>Офис, аренда помещений, хоз.</t>
+          <t>Офис, аренда, содержание</t>
         </is>
       </c>
       <c r="Q61" s="55" t="inlineStr">
@@ -8286,7 +8320,7 @@
       </c>
       <c r="O63" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P63" s="55" t="inlineStr">
@@ -8428,12 +8462,12 @@
       </c>
       <c r="O65" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P65" s="55" t="inlineStr">
         <is>
-          <t>Связь и ИТ</t>
+          <t>Связь, ИТ, ПО</t>
         </is>
       </c>
       <c r="Q65" s="55" t="inlineStr">
@@ -8579,7 +8613,7 @@
       </c>
       <c r="P67" s="55" t="inlineStr">
         <is>
-          <t>Ремонт вагонов и узлов</t>
+          <t>Прочие ж/д и ТЭУ услуги</t>
         </is>
       </c>
       <c r="Q67" s="55" t="inlineStr">
@@ -8720,12 +8754,12 @@
       </c>
       <c r="O69" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P69" s="55" t="inlineStr">
         <is>
-          <t>Связь и ИТ</t>
+          <t>Связь, ИТ, ПО</t>
         </is>
       </c>
       <c r="Q69" s="55" t="inlineStr">
@@ -8793,12 +8827,12 @@
       </c>
       <c r="O70" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P70" s="55" t="inlineStr">
         <is>
-          <t>Офис, аренда помещений, хоз.</t>
+          <t>Офис, аренда, содержание</t>
         </is>
       </c>
       <c r="Q70" s="55" t="inlineStr">
@@ -9856,7 +9890,7 @@
       </c>
       <c r="O85" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P85" s="55" t="inlineStr">
@@ -10493,7 +10527,7 @@
       </c>
       <c r="O94" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P94" s="55" t="inlineStr">
@@ -10566,7 +10600,7 @@
       </c>
       <c r="O95" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P95" s="55" t="inlineStr">
@@ -10785,12 +10819,12 @@
       </c>
       <c r="O98" s="55" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Себестоимость</t>
         </is>
       </c>
       <c r="P98" s="55" t="inlineStr">
         <is>
-          <t>Прочие расходы</t>
+          <t>Прочие ж/д и ТЭУ услуги</t>
         </is>
       </c>
       <c r="Q98" s="55" t="inlineStr">
@@ -12262,12 +12296,12 @@
       </c>
       <c r="O119" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P119" s="55" t="inlineStr">
         <is>
-          <t>Связь и ИТ</t>
+          <t>Связь, ИТ, ПО</t>
         </is>
       </c>
       <c r="Q119" s="55" t="inlineStr">
@@ -13037,7 +13071,7 @@
       </c>
       <c r="O130" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P130" s="55" t="inlineStr">
@@ -13110,7 +13144,7 @@
       </c>
       <c r="O131" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P131" s="55" t="inlineStr">
@@ -13897,7 +13931,7 @@
       </c>
       <c r="O142" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P142" s="55" t="inlineStr">
@@ -16291,7 +16325,7 @@
       </c>
       <c r="O176" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P176" s="55" t="inlineStr">
@@ -16644,12 +16678,12 @@
       </c>
       <c r="O181" s="55" t="inlineStr">
         <is>
-          <t>Выручка</t>
+          <t>Финансовые</t>
         </is>
       </c>
       <c r="P181" s="55" t="inlineStr">
         <is>
-          <t>Операционная выручка (ТЭО, вагоны)</t>
+          <t>Возврат выданных займов</t>
         </is>
       </c>
       <c r="Q181" s="55" t="inlineStr">
@@ -17135,7 +17169,7 @@
       </c>
       <c r="O188" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P188" s="55" t="inlineStr">
@@ -17354,12 +17388,12 @@
       </c>
       <c r="O191" s="55" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Себестоимость</t>
         </is>
       </c>
       <c r="P191" s="55" t="inlineStr">
         <is>
-          <t>Прочие расходы</t>
+          <t>Прочие ж/д и ТЭУ услуги</t>
         </is>
       </c>
       <c r="Q191" s="55" t="inlineStr">
@@ -17857,12 +17891,12 @@
       </c>
       <c r="O198" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P198" s="55" t="inlineStr">
         <is>
-          <t>Связь и ИТ</t>
+          <t>Связь, ИТ, ПО</t>
         </is>
       </c>
       <c r="Q198" s="55" t="inlineStr">
@@ -17930,12 +17964,12 @@
       </c>
       <c r="O199" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P199" s="55" t="inlineStr">
         <is>
-          <t>Связь и ИТ</t>
+          <t>Связь, ИТ, ПО</t>
         </is>
       </c>
       <c r="Q199" s="55" t="inlineStr">
@@ -18145,12 +18179,12 @@
       </c>
       <c r="O202" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P202" s="55" t="inlineStr">
         <is>
-          <t>Офис, аренда помещений, хоз.</t>
+          <t>Офис, аренда, содержание</t>
         </is>
       </c>
       <c r="Q202" s="55" t="inlineStr">
@@ -18218,12 +18252,12 @@
       </c>
       <c r="O203" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Себестоимость</t>
         </is>
       </c>
       <c r="P203" s="55" t="inlineStr">
         <is>
-          <t>Зарплата</t>
+          <t>Страхование вагонов</t>
         </is>
       </c>
       <c r="Q203" s="55" t="inlineStr">
@@ -18291,12 +18325,12 @@
       </c>
       <c r="O204" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P204" s="55" t="inlineStr">
         <is>
-          <t>Маркетинг и представит.</t>
+          <t>Маркетинг и реклама</t>
         </is>
       </c>
       <c r="Q204" s="55" t="inlineStr">
@@ -19577,12 +19611,12 @@
       </c>
       <c r="O222" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P222" s="55" t="inlineStr">
         <is>
-          <t>Связь и ИТ</t>
+          <t>Хоз. расходы и материалы</t>
         </is>
       </c>
       <c r="Q222" s="55" t="inlineStr">
@@ -21098,12 +21132,12 @@
       </c>
       <c r="O243" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P243" s="55" t="inlineStr">
         <is>
-          <t>Офис, аренда помещений, хоз.</t>
+          <t>Офис, аренда, содержание</t>
         </is>
       </c>
       <c r="Q243" s="55" t="inlineStr">
@@ -21601,7 +21635,7 @@
       </c>
       <c r="O250" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P250" s="55" t="inlineStr">
@@ -23313,7 +23347,7 @@
       </c>
       <c r="O274" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P274" s="55" t="inlineStr">
@@ -23386,12 +23420,12 @@
       </c>
       <c r="O275" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P275" s="55" t="inlineStr">
         <is>
-          <t>Страхование</t>
+          <t>Командировки и подотчёт</t>
         </is>
       </c>
       <c r="Q275" s="55" t="inlineStr">
@@ -23459,7 +23493,7 @@
       </c>
       <c r="O276" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P276" s="55" t="inlineStr">
@@ -23532,7 +23566,7 @@
       </c>
       <c r="O277" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P277" s="55" t="inlineStr">
@@ -23605,7 +23639,7 @@
       </c>
       <c r="O278" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P278" s="55" t="inlineStr">
@@ -23678,7 +23712,7 @@
       </c>
       <c r="O279" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P279" s="55" t="inlineStr">
@@ -23751,7 +23785,7 @@
       </c>
       <c r="O280" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P280" s="55" t="inlineStr">
@@ -23824,7 +23858,7 @@
       </c>
       <c r="O281" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P281" s="55" t="inlineStr">
@@ -23897,7 +23931,7 @@
       </c>
       <c r="O282" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P282" s="55" t="inlineStr">
@@ -23970,7 +24004,7 @@
       </c>
       <c r="O283" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P283" s="55" t="inlineStr">
@@ -24043,7 +24077,7 @@
       </c>
       <c r="O284" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P284" s="55" t="inlineStr">
@@ -24116,12 +24150,12 @@
       </c>
       <c r="O285" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P285" s="55" t="inlineStr">
         <is>
-          <t>Связь и ИТ</t>
+          <t>Хоз. расходы и материалы</t>
         </is>
       </c>
       <c r="Q285" s="55" t="inlineStr">
@@ -24262,7 +24296,7 @@
       </c>
       <c r="O287" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P287" s="55" t="inlineStr">
@@ -24335,7 +24369,7 @@
       </c>
       <c r="O288" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P288" s="55" t="inlineStr">
@@ -24408,7 +24442,7 @@
       </c>
       <c r="O289" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P289" s="55" t="inlineStr">
@@ -24481,7 +24515,7 @@
       </c>
       <c r="O290" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P290" s="55" t="inlineStr">
@@ -24627,12 +24661,12 @@
       </c>
       <c r="O292" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P292" s="55" t="inlineStr">
         <is>
-          <t>Проф. услуги (бухг./юр./конс.)</t>
+          <t>Командировки и подотчёт</t>
         </is>
       </c>
       <c r="Q292" s="55" t="inlineStr">
@@ -24915,7 +24949,7 @@
       </c>
       <c r="O296" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P296" s="55" t="inlineStr">
@@ -24988,7 +25022,7 @@
       </c>
       <c r="O297" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P297" s="55" t="inlineStr">
@@ -25061,7 +25095,7 @@
       </c>
       <c r="O298" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P298" s="55" t="inlineStr">
@@ -25134,7 +25168,7 @@
       </c>
       <c r="O299" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P299" s="55" t="inlineStr">
@@ -25276,7 +25310,7 @@
       </c>
       <c r="O301" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P301" s="55" t="inlineStr">
@@ -25422,12 +25456,12 @@
       </c>
       <c r="O303" s="55" t="inlineStr">
         <is>
-          <t>Админ/офис</t>
+          <t>Админ/хоз</t>
         </is>
       </c>
       <c r="P303" s="55" t="inlineStr">
         <is>
-          <t>Офис, аренда помещений, хоз.</t>
+          <t>Офис, аренда, содержание</t>
         </is>
       </c>
       <c r="Q303" s="55" t="inlineStr">
@@ -27581,7 +27615,7 @@
       </c>
       <c r="O334" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P334" s="55" t="inlineStr">
@@ -27857,7 +27891,7 @@
       </c>
       <c r="O338" s="55" t="inlineStr">
         <is>
-          <t>ФОТ</t>
+          <t>Командировки</t>
         </is>
       </c>
       <c r="P338" s="55" t="inlineStr">
@@ -33642,12 +33676,12 @@
       </c>
       <c r="O423" s="55" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Финансовые</t>
         </is>
       </c>
       <c r="P423" s="55" t="inlineStr">
         <is>
-          <t>Прочие расходы</t>
+          <t>Банковские комиссии</t>
         </is>
       </c>
       <c r="Q423" s="55" t="inlineStr">

--- a/waystar-management-report/WayStar_Управленка_Июль2026.xlsx
+++ b/waystar-management-report/WayStar_Управленка_Июль2026.xlsx
@@ -913,7 +913,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Операционный ден. поток</t>
+          <t>Заработано деньгами за месяц</t>
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
@@ -931,8 +931,8 @@
       <c r="F9" s="5" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="6">
-        <f>'ОДДС'!C13</f>
+      <c r="A10" s="8">
+        <f>'ОДДС'!C31</f>
         <v/>
       </c>
       <c r="B10" s="7" t="n"/>
@@ -950,7 +950,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>от операц. деятельности</t>
+          <t>на депозите/прочих счетах Группы</t>
         </is>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -1599,7 +1599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -1916,54 +1916,65 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="inlineStr">
-        <is>
-          <t>Перемещения на прочие счета Группы + конвертация валют (нетто)</t>
-        </is>
-      </c>
-      <c r="C31" s="21">
+      <c r="A31" s="33">
+        <f> ЧИСТЫЙ ДЕНЕЖНЫЙ ПОТОК ЗА ПЕРИОД (заработано деньгами)</f>
+        <v/>
+      </c>
+      <c r="B31" s="25" t="n"/>
+      <c r="C31" s="26">
+        <f>C13+C17+C24+C30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>Размещено на депозит / прочие счета Группы + конвертация (нетто)</t>
+        </is>
+      </c>
+      <c r="C32" s="21">
         <f>(SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$N$5:$N$442,"Внутренний перевод")-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Внутренний перевод"))+(SUMIFS('Реестр операций'!$M$5:$M$442,'Реестр операций'!$N$5:$N$442,"Конвертация валют")-SUMIFS('Реестр операций'!$L$5:$L$442,'Реестр операций'!$N$5:$N$442,"Конвертация валют"))</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="33" t="inlineStr">
-        <is>
-          <t>ЧИСТОЕ ИЗМЕНЕНИЕ ДЕНЕЖНЫХ СРЕДСТВ</t>
-        </is>
-      </c>
-      <c r="B32" s="25" t="n"/>
-      <c r="C32" s="26">
-        <f>C13+C17+C24+C30+C31</f>
-        <v/>
-      </c>
-    </row>
     <row r="33">
       <c r="A33" s="33" t="inlineStr">
         <is>
-          <t>Остаток денежных средств на конец периода</t>
+          <t>Изменение остатка на 5 расчётных счетах</t>
         </is>
       </c>
       <c r="B33" s="25" t="n"/>
       <c r="C33" s="26">
-        <f>C5+C32</f>
+        <f>C31+C32</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="44" customHeight="1">
-      <c r="A35" s="29" t="inlineStr">
-        <is>
-          <t>Сверка сходится: остаток на начало 73 256 ₸ + чистое изменение = остаток на конец ≈ 0 (см. лист «Денежные средства»). Строка «Перемещения на прочие счета Группы + конвертация» балансирует переводы на счета вне этих выписок и курсовые разницы. Все суммы — формулы по реестру.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
+    <row r="34">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
+          <t>Остаток на 5 расчётных счетах на конец периода</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="n"/>
+      <c r="C34" s="26">
+        <f>C5+C33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="44" customHeight="1">
+      <c r="A36" s="29" t="inlineStr">
+        <is>
+          <t>ВАЖНО: за месяц бизнес заработал деньгами +17,9 млн ₸ (чистый денежный поток). Эти деньги переведены на депозитный и прочие счета Группы (вне этих 5 выписок), поэтому 5 расчётных счетов закрылись в 0. То есть «0 на конец» — это только по расчётным счетам; реально накопленные +17,9 млн лежат на депозите/прочих счетах. Пришлите выписки по ним — и остаток раскроется. Все суммы — формулы по реестру.</t>
+        </is>
+      </c>
+    </row>
     <row r="37"/>
+    <row r="38"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A36:C38"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A35:C37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
